--- a/file/Field_Service_Mobile_Android_VPATJ06250.xlsx
+++ b/file/Field_Service_Mobile_Android_VPATJ06250.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
-  <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1C73213A-7F95-414E-B297-1AE203A8C201}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2671AB07-2054-4F33-90D0-27D0401C59F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="740" windowWidth="22540" windowHeight="14300" xr2:uid="{3EB26FA0-8574-43DD-9DF1-88152BDD23AF}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{23E58D6C-7F8C-48E3-B36B-EC58C8E9236F}"/>
   </bookViews>
   <sheets>
-    <sheet name="情報アクセシビリティ自己評価様式" sheetId="1" r:id="rId1"/>
-    <sheet name="様式作成時の技術基準" sheetId="2" r:id="rId2"/>
+    <sheet name="情報アクセシビリティ自己評価様式" sheetId="2" r:id="rId1"/>
+    <sheet name="様式作成時の技術基準" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">様式作成時の技術基準!$A$1:$M$90</definedName>
@@ -30,6 +30,9 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="2"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
@@ -55,7 +58,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
@@ -65,16 +68,16 @@
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>2024</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
+      <t>2026</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
@@ -84,7 +87,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
@@ -93,7 +96,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
@@ -103,16 +106,16 @@
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>12</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
+      <t>21</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
@@ -139,7 +142,7 @@
     <r>
       <rPr>
         <b/>
-        <sz val="11"/>
+        <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
@@ -151,7 +154,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
@@ -168,7 +171,7 @@
     <phoneticPr fontId="4"/>
   </si>
   <si>
-    <t>Field Service Mobile_x000D_
+    <t>Field Service Mobile
 (Android)</t>
   </si>
   <si>
@@ -178,7 +181,7 @@
     <r>
       <rPr>
         <b/>
-        <sz val="11"/>
+        <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
@@ -195,7 +198,7 @@
     <r>
       <rPr>
         <b/>
-        <sz val="11"/>
+        <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
@@ -211,7 +214,7 @@
     <r>
       <rPr>
         <b/>
-        <sz val="11"/>
+        <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
@@ -226,104 +229,98 @@
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="10.5"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>は、技術者が</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
+      <t>は、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>Dynamics 365</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
+      <t xml:space="preserve">Dynamics 365 Field Service </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>の作業指示書や顧客資産、アカウント、連絡先を確認するためのモバイルアプリです。※下記</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>URL</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
+      <t>のモバイルアプリとして、技術者が作業指示、顧客資産、アカウント、連絡先を確認できるよう最適化されています。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>は英語サイトにつながります。</t>
-    </r>
+      <t>問合せ先</t>
+    </r>
+  </si>
+  <si>
+    <t>0120-167-400</t>
     <phoneticPr fontId="4"/>
   </si>
   <si>
     <r>
       <rPr>
         <b/>
-        <sz val="11"/>
+        <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>問合せ先</t>
-    </r>
-  </si>
-  <si>
-    <t>0120-167-400</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
+      <t>ウェブサイト</t>
+    </r>
     <r>
       <rPr>
         <b/>
-        <sz val="11"/>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>URL</t>
+    </r>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/ja-jp/dynamics365/field-service/mobile/overview</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>ウェブサイト</t>
-    </r>
+      <t>機能性能</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>URL</t>
-    </r>
-  </si>
-  <si>
-    <t>https://learn.microsoft.com/ja-jp/dynamics365/field-service/mobile/overview</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
+        <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>機能性能</t>
+      <t>配慮対象アクセス</t>
     </r>
   </si>
   <si>
@@ -336,7 +333,7 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>配慮対象アクセス</t>
+      <t>評価結果</t>
     </r>
   </si>
   <si>
@@ -349,7 +346,7 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>評価結果</t>
+      <t>概要</t>
     </r>
   </si>
   <si>
@@ -362,425 +359,431 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>概要</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
+      <t>視力なしでの使用（全盲）</t>
+    </r>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
         <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>視力なしでの使用（全盲）</t>
-    </r>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
+      <t>対応している</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>対応している</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
+      <t>すべての製品において要件を満たす。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>すべての製品において要件を満たす。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
+      <t>製品・サービスが視覚的な操作モードで提供される場合、視力を必要としない操作モードが用意されているか</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
         <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>製品・サービスが視覚的な操作モードで提供される場合、視力を必要としない操作モードが用意されているか</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
+      <t>限られた視力での使用（弱視、ロービジョン）</t>
+    </r>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
         <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>限られた視力での使用（弱視、ロービジョン）</t>
-    </r>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
+      <t>製品・サービスが視覚的な操作モードで提供される場合、限られた視力で対応可能な操作モードが用意されているか</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
         <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>製品・サービスが視覚的な操作モードで提供される場合、限られた視力で対応可能な操作モードが用意されているか</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
+      <t>色知覚なしでの使用</t>
+    </r>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
         <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>色知覚なしでの使用</t>
-    </r>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
+      <t>評価不要</t>
+    </r>
+    <rPh sb="0" eb="4">
+      <t>ヒョウカフヨウ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>評価不要</t>
-    </r>
-    <rPh sb="0" eb="4">
-      <t>ヒョウカフヨウ</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
+      <t>米国リハビリテーション法</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>508</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>米国リハビリテーション法</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>508</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
+      <t>条を用いているため評価の対象外である。</t>
+    </r>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>条を用いているため評価の対象外である。</t>
-    </r>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
+      <t>製品・サービスが視覚的な操作モードで提供される場合、色知覚を必要としない操作モードが用意されているか</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
         <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>製品・サービスが視覚的な操作モードで提供される場合、色知覚を必要としない操作モードが用意されているか</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
+      <t>聴力なしでの使用（全ろう）</t>
+    </r>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
         <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>聴力なしでの使用（全ろう）</t>
-    </r>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
+      <t>製品・サービスが聴覚的な操作モードで提供される場合、聴力を必要としない操作モードが用意されているか</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
         <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>製品・サービスが聴覚的な操作モードで提供される場合、聴力を必要としない操作モードが用意されているか</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
+      <t>限られた聴力での使用（難聴）</t>
+    </r>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
         <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>限られた聴力での使用（難聴）</t>
-    </r>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
+      <t>製品・サービスが聴覚的な操作モードで行われる場合、強化された音声機能によって限られた聴力を補う操作モードが提供されているか</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
         <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>製品・サービスが聴覚的な操作モードで行われる場合、強化された音声機能によって限られた聴力を補う操作モードが提供されているか</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
+      <t>発話能力なしでの使用</t>
+    </r>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
         <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>発話能力なしでの使用</t>
-    </r>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
+      <t>対応している</t>
+    </r>
+    <rPh sb="0" eb="2">
+      <t>タイオウ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>対応している</t>
-    </r>
-    <rPh sb="0" eb="2">
-      <t>タイオウ</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
+      <t>すべての製品において要件を満たす。</t>
+    </r>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>すべての製品において要件を満たす。</t>
-    </r>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
+      <t>製品・サービスが発話による操作モードで行われる場合、音声入力を必要としない操作モードが用意されているか</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
         <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>製品・サービスが発話による操作モードで行われる場合、音声入力を必要としない操作モードが用意されているか</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
+      <t>限られた器用さ又は力での使用</t>
+    </r>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
         <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>限られた器用さ又は力での使用</t>
-    </r>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
+      <t>製品・サービスが手の動作を必要とする場合、細かい運動制御等を必要としない操作モードが用意されているか</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
         <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>製品・サービスが手の動作を必要とする場合、細かい運動制御等を必要としない操作モードが用意されているか</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
+      <t>限られた手の届く範囲での使用</t>
+    </r>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
         <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>限られた手の届く範囲での使用</t>
-    </r>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
+      <t>製品・サービスが手動による操作モードで提供される場合、手の届く範囲で、かつ限られた力で対応可能な操作モードが用意されているか</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
         <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>製品・サービスが手動による操作モードで提供される場合、手の届く範囲で、かつ限られた力で対応可能な操作モードが用意されているか</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
+      <t>光の点滅による影響の最小化（光感受性発作）</t>
+    </r>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
         <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>光の点滅による影響の最小化（光感受性発作）</t>
-    </r>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
+      <t>対応している</t>
+    </r>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>対応している</t>
-    </r>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
+      <t>すべての製品において要件を満たす。</t>
+    </r>
+    <rPh sb="4" eb="6">
+      <t>セイヒン</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>すべての製品において要件を満たす。</t>
-    </r>
-    <rPh sb="4" eb="6">
-      <t>セイヒン</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
+      <t>製品が視覚的な操作モードで提供される場合、光感受性発作を引き起こすリスクを最小化するような配慮がなされているか</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
         <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>製品が視覚的な操作モードで提供される場合、光感受性発作を引き起こすリスクを最小化するような配慮がなされているか</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
+      <t>プライバシー</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
         <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>プライバシー</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
+      <t>製品・サービスがアクセシビリティ機能を提供する場合、アクセシビリティ機能を使用するにあたりプライバシーが守られる操作モードが用意されているか</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
         <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>製品・サービスがアクセシビリティ機能を提供する場合、アクセシビリティ機能を使用するにあたりプライバシーが守られる操作モードが用意されているか</t>
+      <t>サポート対応　概要</t>
     </r>
   </si>
   <si>
     <r>
       <rPr>
         <b/>
-        <sz val="14"/>
+        <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>サポート対応　概要</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
+      <t>ドキュメントとサポートサービス</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
         <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>ドキュメントとサポートサービス</t>
-    </r>
-  </si>
-  <si>
+      <t>製品の取扱説明書や問合せ先が提供されているか。また、アクセシビリティに配慮したサポート（取扱説明書、電話や手話（筆記）窓口、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>FAX</t>
+    </r>
     <r>
       <rPr>
         <sz val="10.5"/>
@@ -789,69 +792,50 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>製品の取扱説明書や問合せ先が提供されているか。また、アクセシビリティに配慮したサポート（取扱説明書、電話や手話（筆記）窓口、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>FAX</t>
-    </r>
-    <r>
-      <rPr>
+      <t>等）が提供されているか。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
         <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>等）が提供されているか。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
+      <t>用いた技術基準</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>用いた技術基準</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
+      <t>米国リハビリテーション法</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>508</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>米国リハビリテーション法</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>508</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
       <t>条</t>
     </r>
     <phoneticPr fontId="4"/>
@@ -860,7 +844,7 @@
     <r>
       <rPr>
         <b/>
-        <sz val="11"/>
+        <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
@@ -1625,7 +1609,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1666,19 +1650,26 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="10.5"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="10.5"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="10.5"/>
       <color rgb="FF000000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <family val="3"/>
@@ -1701,38 +1692,6 @@
     </font>
     <font>
       <b/>
-      <sz val="28"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10.5"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
       <sz val="10.5"/>
       <color rgb="FF000000"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -1740,17 +1699,35 @@
       <charset val="128"/>
     </font>
     <font>
-      <sz val="10.5"/>
+      <b/>
+      <sz val="28"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="10.5"/>
-      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
       <name val="ＭＳ Ｐゴシック"/>
       <family val="3"/>
       <charset val="128"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10.5"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -2080,188 +2057,197 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -2285,16 +2271,16 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2631,752 +2617,758 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42B79ECA-0407-4A6E-A4CF-1050802D42F5}">
-  <sheetPr codeName="Sheet596">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F295BB76-5DC3-4381-8978-0FC317CC5281}">
+  <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I54"/>
   <sheetFormatPr defaultColWidth="8.58203125" defaultRowHeight="14.5" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="20.08203125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="13.08203125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="10.33203125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="18.58203125" style="2" customWidth="1"/>
-    <col min="5" max="7" width="9.08203125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="8.58203125" style="2"/>
-    <col min="9" max="9" width="28.33203125" style="2" customWidth="1"/>
-    <col min="10" max="16384" width="8.58203125" style="2"/>
+    <col min="1" max="1" width="20.08203125" style="3" customWidth="1"/>
+    <col min="2" max="2" width="13.08203125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="10.33203125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="18.58203125" style="3" customWidth="1"/>
+    <col min="5" max="7" width="9.08203125" style="3" customWidth="1"/>
+    <col min="8" max="8" width="8.58203125" style="3"/>
+    <col min="9" max="9" width="28.33203125" style="3" customWidth="1"/>
+    <col min="10" max="16384" width="8.58203125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="18.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="4"/>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="5" t="s">
+      <c r="A3" s="5"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="5"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="10" t="s">
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="11"/>
-      <c r="I4" s="12"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="13"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="13"/>
-      <c r="B5" s="14"/>
-      <c r="C5" s="15"/>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="16"/>
-      <c r="H5" s="17"/>
-      <c r="I5" s="18"/>
+      <c r="A5" s="14"/>
+      <c r="B5" s="15"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="17"/>
+      <c r="H5" s="18"/>
+      <c r="I5" s="19"/>
     </row>
     <row r="6" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="16"/>
-      <c r="H6" s="17"/>
-      <c r="I6" s="18"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="17"/>
+      <c r="H6" s="18"/>
+      <c r="I6" s="19"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="13"/>
-      <c r="B7" s="14"/>
-      <c r="C7" s="15"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="16"/>
-      <c r="H7" s="17"/>
-      <c r="I7" s="18"/>
+      <c r="A7" s="14"/>
+      <c r="B7" s="15"/>
+      <c r="C7" s="16"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="16"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="17"/>
+      <c r="H7" s="18"/>
+      <c r="I7" s="19"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="16"/>
-      <c r="H8" s="17"/>
-      <c r="I8" s="18"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="10"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="17"/>
+      <c r="H8" s="18"/>
+      <c r="I8" s="19"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="13"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="15"/>
-      <c r="D9" s="15"/>
-      <c r="E9" s="15"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="16"/>
-      <c r="H9" s="17"/>
-      <c r="I9" s="18"/>
+      <c r="A9" s="14"/>
+      <c r="B9" s="15"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="17"/>
+      <c r="H9" s="18"/>
+      <c r="I9" s="19"/>
     </row>
     <row r="10" spans="1:9" ht="54" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="19" t="s">
+      <c r="B10" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="20"/>
-      <c r="D10" s="20"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="16"/>
-      <c r="H10" s="17"/>
-      <c r="I10" s="18"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="22"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="17"/>
+      <c r="H10" s="18"/>
+      <c r="I10" s="19"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="13"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="15"/>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="16"/>
-      <c r="H11" s="17"/>
-      <c r="I11" s="18"/>
+      <c r="A11" s="14"/>
+      <c r="B11" s="15"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="17"/>
+      <c r="H11" s="18"/>
+      <c r="I11" s="19"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="16"/>
-      <c r="H12" s="17"/>
-      <c r="I12" s="18"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="17"/>
+      <c r="H12" s="18"/>
+      <c r="I12" s="19"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="13"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="15"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="16"/>
-      <c r="H13" s="17"/>
-      <c r="I13" s="18"/>
+      <c r="A13" s="14"/>
+      <c r="B13" s="15"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="17"/>
+      <c r="H13" s="18"/>
+      <c r="I13" s="19"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="22" t="s">
+      <c r="B14" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="23"/>
-      <c r="H14" s="24"/>
-      <c r="I14" s="25"/>
+      <c r="C14" s="24"/>
+      <c r="D14" s="24"/>
+      <c r="E14" s="25"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="26"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="27"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="4"/>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
-      <c r="I15" s="4"/>
-    </row>
-    <row r="16" spans="1:9" ht="18.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="26" t="s">
+      <c r="A15" s="5"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4"/>
-      <c r="I16" s="4"/>
+      <c r="B16" s="5"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="27" t="s">
+      <c r="A17" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="28"/>
-      <c r="C17" s="29"/>
-      <c r="D17" s="30" t="s">
+      <c r="B17" s="30"/>
+      <c r="C17" s="31"/>
+      <c r="D17" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="E17" s="31" t="s">
+      <c r="E17" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="F17" s="31"/>
-      <c r="G17" s="31"/>
-      <c r="H17" s="31"/>
-      <c r="I17" s="31"/>
+      <c r="F17" s="33"/>
+      <c r="G17" s="33"/>
+      <c r="H17" s="33"/>
+      <c r="I17" s="33"/>
     </row>
     <row r="18" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="32" t="s">
+      <c r="A18" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="B18" s="33"/>
-      <c r="C18" s="34"/>
-      <c r="D18" s="35" t="s">
+      <c r="B18" s="35"/>
+      <c r="C18" s="36"/>
+      <c r="D18" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="E18" s="36" t="s">
+      <c r="E18" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="F18" s="37"/>
-      <c r="G18" s="37"/>
-      <c r="H18" s="37"/>
-      <c r="I18" s="38"/>
+      <c r="F18" s="39"/>
+      <c r="G18" s="39"/>
+      <c r="H18" s="39"/>
+      <c r="I18" s="40"/>
     </row>
     <row r="19" spans="1:9" ht="50.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="39" t="s">
+      <c r="A19" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="40"/>
-      <c r="C19" s="41"/>
-      <c r="D19" s="42"/>
-      <c r="E19" s="43"/>
-      <c r="F19" s="44"/>
-      <c r="G19" s="44"/>
-      <c r="H19" s="44"/>
-      <c r="I19" s="45"/>
+      <c r="B19" s="42"/>
+      <c r="C19" s="43"/>
+      <c r="D19" s="44"/>
+      <c r="E19" s="45"/>
+      <c r="F19" s="46"/>
+      <c r="G19" s="46"/>
+      <c r="H19" s="46"/>
+      <c r="I19" s="47"/>
     </row>
     <row r="20" spans="1:9" ht="25.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="32" t="s">
+      <c r="A20" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="33"/>
-      <c r="C20" s="34"/>
-      <c r="D20" s="46" t="s">
+      <c r="B20" s="35"/>
+      <c r="C20" s="36"/>
+      <c r="D20" s="48" t="s">
         <v>20</v>
       </c>
-      <c r="E20" s="36" t="s">
+      <c r="E20" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="F20" s="37"/>
-      <c r="G20" s="37"/>
-      <c r="H20" s="37"/>
-      <c r="I20" s="38"/>
+      <c r="F20" s="39"/>
+      <c r="G20" s="39"/>
+      <c r="H20" s="39"/>
+      <c r="I20" s="40"/>
     </row>
     <row r="21" spans="1:9" ht="44.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="39" t="s">
+      <c r="A21" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="B21" s="40"/>
-      <c r="C21" s="41"/>
-      <c r="D21" s="47"/>
-      <c r="E21" s="43"/>
-      <c r="F21" s="44"/>
-      <c r="G21" s="44"/>
-      <c r="H21" s="44"/>
-      <c r="I21" s="45"/>
+      <c r="B21" s="42"/>
+      <c r="C21" s="43"/>
+      <c r="D21" s="49"/>
+      <c r="E21" s="45"/>
+      <c r="F21" s="46"/>
+      <c r="G21" s="46"/>
+      <c r="H21" s="46"/>
+      <c r="I21" s="47"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="32" t="s">
+      <c r="A22" s="34" t="s">
         <v>25</v>
       </c>
-      <c r="B22" s="33"/>
-      <c r="C22" s="34"/>
-      <c r="D22" s="42" t="s">
+      <c r="B22" s="35"/>
+      <c r="C22" s="36"/>
+      <c r="D22" s="44" t="s">
         <v>26</v>
       </c>
-      <c r="E22" s="42" t="s">
+      <c r="E22" s="44" t="s">
         <v>27</v>
       </c>
-      <c r="F22" s="42"/>
-      <c r="G22" s="42"/>
-      <c r="H22" s="42"/>
-      <c r="I22" s="42"/>
+      <c r="F22" s="44"/>
+      <c r="G22" s="44"/>
+      <c r="H22" s="44"/>
+      <c r="I22" s="44"/>
     </row>
     <row r="23" spans="1:9" ht="51.65" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="39" t="s">
+      <c r="A23" s="41" t="s">
         <v>28</v>
       </c>
-      <c r="B23" s="40"/>
-      <c r="C23" s="41"/>
-      <c r="D23" s="42"/>
-      <c r="E23" s="42"/>
-      <c r="F23" s="42"/>
-      <c r="G23" s="42"/>
-      <c r="H23" s="42"/>
-      <c r="I23" s="42"/>
+      <c r="B23" s="42"/>
+      <c r="C23" s="43"/>
+      <c r="D23" s="44"/>
+      <c r="E23" s="44"/>
+      <c r="F23" s="44"/>
+      <c r="G23" s="44"/>
+      <c r="H23" s="44"/>
+      <c r="I23" s="44"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="32" t="s">
+      <c r="A24" s="34" t="s">
         <v>29</v>
       </c>
-      <c r="B24" s="33"/>
-      <c r="C24" s="34"/>
-      <c r="D24" s="35" t="s">
+      <c r="B24" s="35"/>
+      <c r="C24" s="36"/>
+      <c r="D24" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="E24" s="35" t="s">
+      <c r="E24" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="F24" s="35"/>
-      <c r="G24" s="35"/>
-      <c r="H24" s="35"/>
-      <c r="I24" s="35"/>
+      <c r="F24" s="39"/>
+      <c r="G24" s="39"/>
+      <c r="H24" s="39"/>
+      <c r="I24" s="40"/>
     </row>
     <row r="25" spans="1:9" ht="51" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="39" t="s">
+      <c r="A25" s="41" t="s">
         <v>30</v>
       </c>
-      <c r="B25" s="40"/>
-      <c r="C25" s="41"/>
-      <c r="D25" s="42"/>
-      <c r="E25" s="35"/>
-      <c r="F25" s="35"/>
-      <c r="G25" s="35"/>
-      <c r="H25" s="35"/>
-      <c r="I25" s="35"/>
+      <c r="B25" s="42"/>
+      <c r="C25" s="43"/>
+      <c r="D25" s="44"/>
+      <c r="E25" s="45"/>
+      <c r="F25" s="46"/>
+      <c r="G25" s="46"/>
+      <c r="H25" s="46"/>
+      <c r="I25" s="47"/>
     </row>
     <row r="26" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="32" t="s">
+      <c r="A26" s="34" t="s">
         <v>31</v>
       </c>
-      <c r="B26" s="33"/>
-      <c r="C26" s="34"/>
-      <c r="D26" s="35" t="s">
+      <c r="B26" s="35"/>
+      <c r="C26" s="36"/>
+      <c r="D26" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="E26" s="35" t="s">
+      <c r="E26" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="F26" s="35"/>
-      <c r="G26" s="35"/>
-      <c r="H26" s="35"/>
-      <c r="I26" s="35"/>
+      <c r="F26" s="39"/>
+      <c r="G26" s="39"/>
+      <c r="H26" s="39"/>
+      <c r="I26" s="40"/>
     </row>
     <row r="27" spans="1:9" ht="51.65" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" s="39" t="s">
+      <c r="A27" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="B27" s="40"/>
-      <c r="C27" s="41"/>
-      <c r="D27" s="42"/>
-      <c r="E27" s="35"/>
-      <c r="F27" s="35"/>
-      <c r="G27" s="35"/>
-      <c r="H27" s="35"/>
-      <c r="I27" s="35"/>
+      <c r="B27" s="42"/>
+      <c r="C27" s="43"/>
+      <c r="D27" s="44"/>
+      <c r="E27" s="45"/>
+      <c r="F27" s="46"/>
+      <c r="G27" s="46"/>
+      <c r="H27" s="46"/>
+      <c r="I27" s="47"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" s="32" t="s">
+      <c r="A28" s="34" t="s">
         <v>33</v>
       </c>
-      <c r="B28" s="33"/>
-      <c r="C28" s="34"/>
-      <c r="D28" s="46" t="s">
+      <c r="B28" s="35"/>
+      <c r="C28" s="36"/>
+      <c r="D28" s="48" t="s">
         <v>34</v>
       </c>
-      <c r="E28" s="42" t="s">
+      <c r="E28" s="44" t="s">
         <v>35</v>
       </c>
-      <c r="F28" s="42"/>
-      <c r="G28" s="42"/>
-      <c r="H28" s="42"/>
-      <c r="I28" s="42"/>
+      <c r="F28" s="44"/>
+      <c r="G28" s="44"/>
+      <c r="H28" s="44"/>
+      <c r="I28" s="44"/>
     </row>
     <row r="29" spans="1:9" ht="51.65" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="39" t="s">
+      <c r="A29" s="41" t="s">
         <v>36</v>
       </c>
-      <c r="B29" s="40"/>
-      <c r="C29" s="41"/>
-      <c r="D29" s="47"/>
-      <c r="E29" s="42"/>
-      <c r="F29" s="42"/>
-      <c r="G29" s="42"/>
-      <c r="H29" s="42"/>
-      <c r="I29" s="42"/>
+      <c r="B29" s="42"/>
+      <c r="C29" s="43"/>
+      <c r="D29" s="49"/>
+      <c r="E29" s="44"/>
+      <c r="F29" s="44"/>
+      <c r="G29" s="44"/>
+      <c r="H29" s="44"/>
+      <c r="I29" s="44"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="32" t="s">
+      <c r="A30" s="34" t="s">
         <v>37</v>
       </c>
-      <c r="B30" s="33"/>
-      <c r="C30" s="34"/>
-      <c r="D30" s="46" t="s">
+      <c r="B30" s="35"/>
+      <c r="C30" s="36"/>
+      <c r="D30" s="48" t="s">
         <v>20</v>
       </c>
-      <c r="E30" s="36" t="s">
+      <c r="E30" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="37"/>
-      <c r="G30" s="37"/>
-      <c r="H30" s="37"/>
-      <c r="I30" s="38"/>
+      <c r="F30" s="39"/>
+      <c r="G30" s="39"/>
+      <c r="H30" s="39"/>
+      <c r="I30" s="40"/>
     </row>
     <row r="31" spans="1:9" ht="51.65" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="39" t="s">
+      <c r="A31" s="41" t="s">
         <v>38</v>
       </c>
-      <c r="B31" s="40"/>
-      <c r="C31" s="41"/>
-      <c r="D31" s="48"/>
-      <c r="E31" s="49"/>
-      <c r="F31" s="50"/>
-      <c r="G31" s="50"/>
-      <c r="H31" s="50"/>
-      <c r="I31" s="51"/>
+      <c r="B31" s="42"/>
+      <c r="C31" s="43"/>
+      <c r="D31" s="50"/>
+      <c r="E31" s="51"/>
+      <c r="F31" s="52"/>
+      <c r="G31" s="52"/>
+      <c r="H31" s="52"/>
+      <c r="I31" s="53"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="32" t="s">
+      <c r="A32" s="34" t="s">
         <v>39</v>
       </c>
-      <c r="B32" s="33"/>
-      <c r="C32" s="34"/>
-      <c r="D32" s="48"/>
-      <c r="E32" s="49"/>
-      <c r="F32" s="50"/>
-      <c r="G32" s="50"/>
-      <c r="H32" s="50"/>
-      <c r="I32" s="51"/>
+      <c r="B32" s="35"/>
+      <c r="C32" s="36"/>
+      <c r="D32" s="50"/>
+      <c r="E32" s="51"/>
+      <c r="F32" s="52"/>
+      <c r="G32" s="52"/>
+      <c r="H32" s="52"/>
+      <c r="I32" s="53"/>
     </row>
     <row r="33" spans="1:9" ht="69.650000000000006" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="39" t="s">
+      <c r="A33" s="41" t="s">
         <v>40</v>
       </c>
-      <c r="B33" s="40"/>
-      <c r="C33" s="41"/>
-      <c r="D33" s="47"/>
-      <c r="E33" s="43"/>
-      <c r="F33" s="44"/>
-      <c r="G33" s="44"/>
-      <c r="H33" s="44"/>
-      <c r="I33" s="45"/>
+      <c r="B33" s="42"/>
+      <c r="C33" s="43"/>
+      <c r="D33" s="49"/>
+      <c r="E33" s="45"/>
+      <c r="F33" s="46"/>
+      <c r="G33" s="46"/>
+      <c r="H33" s="46"/>
+      <c r="I33" s="47"/>
     </row>
     <row r="34" spans="1:9" ht="25.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="32" t="s">
+      <c r="A34" s="34" t="s">
         <v>41</v>
       </c>
-      <c r="B34" s="33"/>
-      <c r="C34" s="34"/>
-      <c r="D34" s="42" t="s">
+      <c r="B34" s="35"/>
+      <c r="C34" s="36"/>
+      <c r="D34" s="44" t="s">
         <v>42</v>
       </c>
-      <c r="E34" s="42" t="s">
+      <c r="E34" s="44" t="s">
         <v>43</v>
       </c>
-      <c r="F34" s="42"/>
-      <c r="G34" s="42"/>
-      <c r="H34" s="42"/>
-      <c r="I34" s="42"/>
+      <c r="F34" s="44"/>
+      <c r="G34" s="44"/>
+      <c r="H34" s="44"/>
+      <c r="I34" s="44"/>
     </row>
     <row r="35" spans="1:9" ht="51.65" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" s="39" t="s">
+      <c r="A35" s="41" t="s">
         <v>44</v>
       </c>
-      <c r="B35" s="40"/>
-      <c r="C35" s="41"/>
-      <c r="D35" s="42"/>
-      <c r="E35" s="42"/>
-      <c r="F35" s="42"/>
-      <c r="G35" s="42"/>
-      <c r="H35" s="42"/>
-      <c r="I35" s="42"/>
+      <c r="B35" s="42"/>
+      <c r="C35" s="43"/>
+      <c r="D35" s="44"/>
+      <c r="E35" s="44"/>
+      <c r="F35" s="44"/>
+      <c r="G35" s="44"/>
+      <c r="H35" s="44"/>
+      <c r="I35" s="44"/>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="52"/>
-      <c r="B36" s="52"/>
-      <c r="C36" s="52"/>
-      <c r="D36" s="53"/>
-      <c r="E36" s="53"/>
-      <c r="F36" s="53"/>
-      <c r="G36" s="53"/>
-      <c r="H36" s="53"/>
-      <c r="I36" s="53"/>
+      <c r="A36" s="54"/>
+      <c r="B36" s="54"/>
+      <c r="C36" s="54"/>
+      <c r="D36" s="55"/>
+      <c r="E36" s="55"/>
+      <c r="F36" s="55"/>
+      <c r="G36" s="55"/>
+      <c r="H36" s="55"/>
+      <c r="I36" s="55"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="27" t="s">
+      <c r="A37" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="B37" s="28"/>
-      <c r="C37" s="29"/>
-      <c r="D37" s="30" t="s">
+      <c r="B37" s="30"/>
+      <c r="C37" s="31"/>
+      <c r="D37" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="E37" s="31" t="s">
+      <c r="E37" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="F37" s="31"/>
-      <c r="G37" s="31"/>
-      <c r="H37" s="31"/>
-      <c r="I37" s="31"/>
+      <c r="F37" s="33"/>
+      <c r="G37" s="33"/>
+      <c r="H37" s="33"/>
+      <c r="I37" s="33"/>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38" s="32" t="s">
+      <c r="A38" s="34" t="s">
         <v>45</v>
       </c>
-      <c r="B38" s="33"/>
-      <c r="C38" s="34"/>
-      <c r="D38" s="42" t="s">
+      <c r="B38" s="35"/>
+      <c r="C38" s="36"/>
+      <c r="D38" s="44" t="s">
         <v>42</v>
       </c>
-      <c r="E38" s="42" t="s">
+      <c r="E38" s="44" t="s">
         <v>43</v>
       </c>
-      <c r="F38" s="42"/>
-      <c r="G38" s="42"/>
-      <c r="H38" s="42"/>
-      <c r="I38" s="42"/>
+      <c r="F38" s="44"/>
+      <c r="G38" s="44"/>
+      <c r="H38" s="44"/>
+      <c r="I38" s="44"/>
     </row>
     <row r="39" spans="1:9" ht="64.400000000000006" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39" s="39" t="s">
+      <c r="A39" s="41" t="s">
         <v>46</v>
       </c>
-      <c r="B39" s="40"/>
-      <c r="C39" s="41"/>
-      <c r="D39" s="42"/>
-      <c r="E39" s="42"/>
-      <c r="F39" s="42"/>
-      <c r="G39" s="42"/>
-      <c r="H39" s="42"/>
-      <c r="I39" s="42"/>
+      <c r="B39" s="42"/>
+      <c r="C39" s="43"/>
+      <c r="D39" s="44"/>
+      <c r="E39" s="44"/>
+      <c r="F39" s="44"/>
+      <c r="G39" s="44"/>
+      <c r="H39" s="44"/>
+      <c r="I39" s="44"/>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" s="4"/>
-      <c r="B40" s="4"/>
-      <c r="C40" s="4"/>
-      <c r="D40" s="4"/>
-      <c r="E40" s="4"/>
-      <c r="F40" s="4"/>
-      <c r="G40" s="4"/>
-      <c r="H40" s="4"/>
-      <c r="I40" s="4"/>
-    </row>
-    <row r="41" spans="1:9" ht="18.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A41" s="26" t="s">
+      <c r="A40" s="5"/>
+      <c r="B40" s="5"/>
+      <c r="C40" s="5"/>
+      <c r="D40" s="5"/>
+      <c r="E40" s="5"/>
+      <c r="F40" s="5"/>
+      <c r="G40" s="5"/>
+      <c r="H40" s="5"/>
+      <c r="I40" s="5"/>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A41" s="28" t="s">
         <v>47</v>
       </c>
-      <c r="B41" s="4"/>
-      <c r="C41" s="4"/>
-      <c r="D41" s="4"/>
-      <c r="E41" s="4"/>
-      <c r="F41" s="4"/>
-      <c r="G41" s="4"/>
-      <c r="H41" s="4"/>
-      <c r="I41" s="4"/>
+      <c r="B41" s="5"/>
+      <c r="C41" s="5"/>
+      <c r="D41" s="5"/>
+      <c r="E41" s="5"/>
+      <c r="F41" s="5"/>
+      <c r="G41" s="5"/>
+      <c r="H41" s="5"/>
+      <c r="I41" s="5"/>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A42" s="27" t="s">
+      <c r="A42" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="B42" s="28"/>
-      <c r="C42" s="29"/>
-      <c r="D42" s="30" t="s">
+      <c r="B42" s="30"/>
+      <c r="C42" s="31"/>
+      <c r="D42" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="E42" s="31" t="s">
+      <c r="E42" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="F42" s="31"/>
-      <c r="G42" s="31"/>
-      <c r="H42" s="31"/>
-      <c r="I42" s="31"/>
+      <c r="F42" s="33"/>
+      <c r="G42" s="33"/>
+      <c r="H42" s="33"/>
+      <c r="I42" s="33"/>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A43" s="32" t="s">
+      <c r="A43" s="34" t="s">
         <v>48</v>
       </c>
-      <c r="B43" s="33"/>
-      <c r="C43" s="34"/>
-      <c r="D43" s="42" t="s">
+      <c r="B43" s="35"/>
+      <c r="C43" s="36"/>
+      <c r="D43" s="44" t="s">
         <v>42</v>
       </c>
-      <c r="E43" s="42" t="s">
+      <c r="E43" s="44" t="s">
         <v>43</v>
       </c>
-      <c r="F43" s="42"/>
-      <c r="G43" s="42"/>
-      <c r="H43" s="42"/>
-      <c r="I43" s="42"/>
+      <c r="F43" s="44"/>
+      <c r="G43" s="44"/>
+      <c r="H43" s="44"/>
+      <c r="I43" s="44"/>
     </row>
     <row r="44" spans="1:9" ht="52.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A44" s="39" t="s">
+      <c r="A44" s="41" t="s">
         <v>49</v>
       </c>
-      <c r="B44" s="40"/>
-      <c r="C44" s="41"/>
-      <c r="D44" s="42"/>
-      <c r="E44" s="42"/>
-      <c r="F44" s="42"/>
-      <c r="G44" s="42"/>
-      <c r="H44" s="42"/>
-      <c r="I44" s="42"/>
+      <c r="B44" s="42"/>
+      <c r="C44" s="43"/>
+      <c r="D44" s="44"/>
+      <c r="E44" s="44"/>
+      <c r="F44" s="44"/>
+      <c r="G44" s="44"/>
+      <c r="H44" s="44"/>
+      <c r="I44" s="44"/>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A45" s="4"/>
-      <c r="B45" s="4"/>
-      <c r="C45" s="4"/>
-      <c r="D45" s="4"/>
-      <c r="E45" s="4"/>
-      <c r="F45" s="4"/>
-      <c r="G45" s="4"/>
-      <c r="H45" s="4"/>
-      <c r="I45" s="4"/>
+      <c r="A45" s="5"/>
+      <c r="B45" s="5"/>
+      <c r="C45" s="5"/>
+      <c r="D45" s="5"/>
+      <c r="E45" s="5"/>
+      <c r="F45" s="5"/>
+      <c r="G45" s="5"/>
+      <c r="H45" s="5"/>
+      <c r="I45" s="5"/>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A46" s="54" t="s">
+      <c r="A46" s="56" t="s">
         <v>50</v>
       </c>
-      <c r="B46" s="42" t="s">
+      <c r="B46" s="44" t="s">
         <v>51</v>
       </c>
-      <c r="C46" s="42"/>
-      <c r="D46" s="42"/>
-      <c r="E46" s="42"/>
-      <c r="F46" s="42"/>
-      <c r="G46" s="42"/>
-      <c r="H46" s="42"/>
-      <c r="I46" s="42"/>
+      <c r="C46" s="44"/>
+      <c r="D46" s="44"/>
+      <c r="E46" s="44"/>
+      <c r="F46" s="44"/>
+      <c r="G46" s="44"/>
+      <c r="H46" s="44"/>
+      <c r="I46" s="44"/>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A47" s="55"/>
-      <c r="B47" s="14"/>
-      <c r="C47" s="15"/>
-      <c r="D47" s="15"/>
-      <c r="E47" s="15"/>
-      <c r="F47" s="4"/>
-      <c r="G47" s="56"/>
-      <c r="H47" s="56"/>
-      <c r="I47" s="57"/>
+      <c r="A47" s="57"/>
+      <c r="B47" s="15"/>
+      <c r="C47" s="16"/>
+      <c r="D47" s="16"/>
+      <c r="E47" s="16"/>
+      <c r="F47" s="5"/>
+      <c r="G47" s="58"/>
+      <c r="H47" s="58"/>
+      <c r="I47" s="59"/>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A48" s="54" t="s">
+      <c r="A48" s="56" t="s">
         <v>52</v>
       </c>
-      <c r="B48" s="42"/>
-      <c r="C48" s="42"/>
-      <c r="D48" s="42"/>
-      <c r="E48" s="42"/>
-      <c r="F48" s="42"/>
-      <c r="G48" s="42"/>
-      <c r="H48" s="42"/>
-      <c r="I48" s="42"/>
-    </row>
-    <row r="49" spans="2:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="B49" s="42"/>
-      <c r="C49" s="42"/>
-      <c r="D49" s="42"/>
-      <c r="E49" s="42"/>
-      <c r="F49" s="42"/>
-      <c r="G49" s="42"/>
-      <c r="H49" s="42"/>
-      <c r="I49" s="42"/>
-    </row>
-    <row r="50" spans="2:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="B50" s="42"/>
-      <c r="C50" s="42"/>
-      <c r="D50" s="42"/>
-      <c r="E50" s="42"/>
-      <c r="F50" s="42"/>
-      <c r="G50" s="42"/>
-      <c r="H50" s="42"/>
-      <c r="I50" s="42"/>
-    </row>
-    <row r="51" spans="2:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="B51" s="42"/>
-      <c r="C51" s="42"/>
-      <c r="D51" s="42"/>
-      <c r="E51" s="42"/>
-      <c r="F51" s="42"/>
-      <c r="G51" s="42"/>
-      <c r="H51" s="42"/>
-      <c r="I51" s="42"/>
-    </row>
-    <row r="52" spans="2:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="B52" s="42"/>
-      <c r="C52" s="42"/>
-      <c r="D52" s="42"/>
-      <c r="E52" s="42"/>
-      <c r="F52" s="42"/>
-      <c r="G52" s="42"/>
-      <c r="H52" s="42"/>
-      <c r="I52" s="42"/>
-    </row>
-    <row r="53" spans="2:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="B53" s="42"/>
-      <c r="C53" s="42"/>
-      <c r="D53" s="42"/>
-      <c r="E53" s="42"/>
-      <c r="F53" s="42"/>
-      <c r="G53" s="42"/>
-      <c r="H53" s="42"/>
-      <c r="I53" s="42"/>
-    </row>
-    <row r="54" spans="2:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="B54" s="42"/>
-      <c r="C54" s="42"/>
-      <c r="D54" s="42"/>
-      <c r="E54" s="42"/>
-      <c r="F54" s="42"/>
-      <c r="G54" s="42"/>
-      <c r="H54" s="42"/>
-      <c r="I54" s="42"/>
+      <c r="B48" s="44"/>
+      <c r="C48" s="44"/>
+      <c r="D48" s="44"/>
+      <c r="E48" s="44"/>
+      <c r="F48" s="44"/>
+      <c r="G48" s="44"/>
+      <c r="H48" s="44"/>
+      <c r="I48" s="44"/>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A49" s="60"/>
+      <c r="B49" s="44"/>
+      <c r="C49" s="44"/>
+      <c r="D49" s="44"/>
+      <c r="E49" s="44"/>
+      <c r="F49" s="44"/>
+      <c r="G49" s="44"/>
+      <c r="H49" s="44"/>
+      <c r="I49" s="44"/>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A50" s="60"/>
+      <c r="B50" s="44"/>
+      <c r="C50" s="44"/>
+      <c r="D50" s="44"/>
+      <c r="E50" s="44"/>
+      <c r="F50" s="44"/>
+      <c r="G50" s="44"/>
+      <c r="H50" s="44"/>
+      <c r="I50" s="44"/>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A51" s="60"/>
+      <c r="B51" s="44"/>
+      <c r="C51" s="44"/>
+      <c r="D51" s="44"/>
+      <c r="E51" s="44"/>
+      <c r="F51" s="44"/>
+      <c r="G51" s="44"/>
+      <c r="H51" s="44"/>
+      <c r="I51" s="44"/>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A52" s="60"/>
+      <c r="B52" s="44"/>
+      <c r="C52" s="44"/>
+      <c r="D52" s="44"/>
+      <c r="E52" s="44"/>
+      <c r="F52" s="44"/>
+      <c r="G52" s="44"/>
+      <c r="H52" s="44"/>
+      <c r="I52" s="44"/>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A53" s="60"/>
+      <c r="B53" s="44"/>
+      <c r="C53" s="44"/>
+      <c r="D53" s="44"/>
+      <c r="E53" s="44"/>
+      <c r="F53" s="44"/>
+      <c r="G53" s="44"/>
+      <c r="H53" s="44"/>
+      <c r="I53" s="44"/>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A54" s="60"/>
+      <c r="B54" s="44"/>
+      <c r="C54" s="44"/>
+      <c r="D54" s="44"/>
+      <c r="E54" s="44"/>
+      <c r="F54" s="44"/>
+      <c r="G54" s="44"/>
+      <c r="H54" s="44"/>
+      <c r="I54" s="44"/>
     </row>
   </sheetData>
   <mergeCells count="58">
@@ -3441,2260 +3433,2261 @@
   </mergeCells>
   <phoneticPr fontId="4"/>
   <hyperlinks>
-    <hyperlink ref="B14" r:id="rId1" xr:uid="{F4FBAFD9-D634-485E-A8A8-C856A2A92EEC}"/>
+    <hyperlink ref="B14" r:id="rId1" display="https://www.microsoft.com/ja-jp/dynamics-365/field-service/field-service-mobile-android" xr:uid="{594506A0-A40C-4170-B3B0-560DD09A490D}"/>
+    <hyperlink ref="B14:E14" r:id="rId2" display="https://learn.microsoft.com/ja-jp/dynamics365/field-service/mobile/overview" xr:uid="{3C37F7CD-7515-4310-9337-E613E40384E8}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="25" orientation="portrait" r:id="rId2"/>
+  <pageSetup paperSize="9" scale="25" orientation="portrait" r:id="rId3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B4BE79B-4E70-4AC9-A93C-76C500D59FC7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E308598-43B8-4EFB-855E-3F9EA4429E87}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:M90"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="15.83203125" style="64" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="51.08203125" style="63" customWidth="1"/>
-    <col min="3" max="3" width="33.08203125" style="63" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" style="67" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="51.08203125" style="66" customWidth="1"/>
+    <col min="3" max="3" width="33.08203125" style="66" customWidth="1"/>
     <col min="4" max="13" width="10.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="71.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1" s="58" t="s">
+      <c r="A1" s="61" t="s">
         <v>53</v>
       </c>
-      <c r="B1" s="59" t="s">
+      <c r="B1" s="62" t="s">
         <v>54</v>
       </c>
-      <c r="C1" s="59" t="s">
+      <c r="C1" s="62" t="s">
         <v>55</v>
       </c>
-      <c r="D1" s="60" t="s">
+      <c r="D1" s="63" t="s">
         <v>56</v>
       </c>
-      <c r="E1" s="59" t="s">
+      <c r="E1" s="62" t="s">
         <v>57</v>
       </c>
-      <c r="F1" s="59" t="s">
+      <c r="F1" s="62" t="s">
         <v>58</v>
       </c>
-      <c r="G1" s="59" t="s">
+      <c r="G1" s="62" t="s">
         <v>59</v>
       </c>
-      <c r="H1" s="59" t="s">
+      <c r="H1" s="62" t="s">
         <v>60</v>
       </c>
-      <c r="I1" s="59" t="s">
+      <c r="I1" s="62" t="s">
         <v>61</v>
       </c>
-      <c r="J1" s="59" t="s">
+      <c r="J1" s="62" t="s">
         <v>62</v>
       </c>
-      <c r="K1" s="59" t="s">
+      <c r="K1" s="62" t="s">
         <v>63</v>
       </c>
-      <c r="L1" s="59" t="s">
+      <c r="L1" s="62" t="s">
         <v>64</v>
       </c>
-      <c r="M1" s="59" t="s">
+      <c r="M1" s="62" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="61">
+      <c r="A2" s="64">
         <v>301</v>
       </c>
-      <c r="B2" s="62" t="s">
+      <c r="B2" s="65" t="s">
         <v>66</v>
       </c>
-      <c r="C2" s="63" t="s">
+      <c r="C2" s="66" t="s">
         <v>67</v>
       </c>
-      <c r="D2" s="64"/>
-      <c r="E2" s="65" t="s">
+      <c r="D2" s="67"/>
+      <c r="E2" s="68" t="s">
         <v>68</v>
       </c>
-      <c r="F2" s="65" t="s">
+      <c r="F2" s="68" t="s">
         <v>68</v>
       </c>
-      <c r="G2" s="66"/>
-      <c r="H2" s="65" t="s">
+      <c r="G2" s="69"/>
+      <c r="H2" s="68" t="s">
         <v>68</v>
       </c>
-      <c r="I2" s="65" t="s">
+      <c r="I2" s="68" t="s">
         <v>68</v>
       </c>
-      <c r="J2" s="65" t="s">
+      <c r="J2" s="68" t="s">
         <v>68</v>
       </c>
-      <c r="K2" s="65" t="s">
+      <c r="K2" s="68" t="s">
         <v>68</v>
       </c>
-      <c r="L2" s="65" t="s">
+      <c r="L2" s="68" t="s">
         <v>68</v>
       </c>
-      <c r="M2" s="65" t="s">
+      <c r="M2" s="68" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="61">
+      <c r="A3" s="64">
         <v>302</v>
       </c>
-      <c r="B3" s="62" t="s">
+      <c r="B3" s="65" t="s">
         <v>69</v>
       </c>
-      <c r="C3" s="63" t="s">
+      <c r="C3" s="66" t="s">
         <v>70</v>
       </c>
-      <c r="D3" s="64"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="66"/>
-      <c r="H3" s="65"/>
-      <c r="I3" s="65"/>
-      <c r="J3" s="65"/>
-      <c r="K3" s="65"/>
-      <c r="L3" s="65"/>
-      <c r="M3" s="65"/>
+      <c r="D3" s="67"/>
+      <c r="E3" s="68"/>
+      <c r="F3" s="68"/>
+      <c r="G3" s="69"/>
+      <c r="H3" s="68"/>
+      <c r="I3" s="68"/>
+      <c r="J3" s="68"/>
+      <c r="K3" s="68"/>
+      <c r="L3" s="68"/>
+      <c r="M3" s="68"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="64">
+      <c r="A4" s="67">
         <v>302.10000000000002</v>
       </c>
-      <c r="B4" s="63" t="s">
+      <c r="B4" s="66" t="s">
         <v>71</v>
       </c>
-      <c r="C4" s="63" t="s">
+      <c r="C4" s="66" t="s">
         <v>72</v>
       </c>
-      <c r="D4" s="64"/>
-      <c r="E4" s="64" t="s">
-        <v>73</v>
-      </c>
-      <c r="F4" s="64"/>
-      <c r="G4" s="67"/>
-      <c r="H4" s="64"/>
-      <c r="I4" s="64"/>
-      <c r="J4" s="64"/>
-      <c r="K4" s="64"/>
-      <c r="L4" s="64"/>
-      <c r="M4" s="64"/>
+      <c r="D4" s="67"/>
+      <c r="E4" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="F4" s="67"/>
+      <c r="G4" s="70"/>
+      <c r="H4" s="67"/>
+      <c r="I4" s="67"/>
+      <c r="J4" s="67"/>
+      <c r="K4" s="67"/>
+      <c r="L4" s="67"/>
+      <c r="M4" s="67"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="64">
+      <c r="A5" s="67">
         <v>302.2</v>
       </c>
-      <c r="B5" s="63" t="s">
+      <c r="B5" s="66" t="s">
         <v>74</v>
       </c>
-      <c r="C5" s="63" t="s">
+      <c r="C5" s="66" t="s">
         <v>75</v>
       </c>
-      <c r="D5" s="64"/>
-      <c r="E5" s="64"/>
-      <c r="F5" s="64" t="s">
-        <v>73</v>
-      </c>
-      <c r="G5" s="67"/>
-      <c r="H5" s="64"/>
-      <c r="I5" s="64"/>
-      <c r="J5" s="64"/>
-      <c r="K5" s="64"/>
-      <c r="L5" s="64"/>
-      <c r="M5" s="64"/>
+      <c r="D5" s="67"/>
+      <c r="E5" s="67"/>
+      <c r="F5" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="G5" s="70"/>
+      <c r="H5" s="67"/>
+      <c r="I5" s="67"/>
+      <c r="J5" s="67"/>
+      <c r="K5" s="67"/>
+      <c r="L5" s="67"/>
+      <c r="M5" s="67"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="64">
+      <c r="A6" s="67">
         <v>302.3</v>
       </c>
-      <c r="B6" s="63" t="s">
+      <c r="B6" s="66" t="s">
         <v>76</v>
       </c>
-      <c r="C6" s="63" t="s">
+      <c r="C6" s="66" t="s">
         <v>77</v>
       </c>
-      <c r="D6" s="64"/>
-      <c r="E6" s="64"/>
-      <c r="F6" s="64" t="s">
-        <v>73</v>
-      </c>
-      <c r="G6" s="67"/>
-      <c r="H6" s="64"/>
-      <c r="I6" s="64"/>
-      <c r="J6" s="64"/>
-      <c r="K6" s="64"/>
-      <c r="L6" s="64"/>
-      <c r="M6" s="64"/>
+      <c r="D6" s="67"/>
+      <c r="E6" s="67"/>
+      <c r="F6" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="G6" s="70"/>
+      <c r="H6" s="67"/>
+      <c r="I6" s="67"/>
+      <c r="J6" s="67"/>
+      <c r="K6" s="67"/>
+      <c r="L6" s="67"/>
+      <c r="M6" s="67"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="64">
+      <c r="A7" s="67">
         <v>302.39999999999998</v>
       </c>
-      <c r="B7" s="63" t="s">
+      <c r="B7" s="66" t="s">
         <v>78</v>
       </c>
-      <c r="C7" s="63" t="s">
+      <c r="C7" s="66" t="s">
         <v>79</v>
       </c>
-      <c r="D7" s="64"/>
-      <c r="E7" s="64"/>
-      <c r="F7" s="64"/>
-      <c r="G7" s="67"/>
-      <c r="H7" s="64" t="s">
-        <v>73</v>
-      </c>
-      <c r="I7" s="64"/>
-      <c r="J7" s="64"/>
-      <c r="K7" s="64"/>
-      <c r="L7" s="64"/>
-      <c r="M7" s="64"/>
+      <c r="D7" s="67"/>
+      <c r="E7" s="67"/>
+      <c r="F7" s="67"/>
+      <c r="G7" s="70"/>
+      <c r="H7" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="I7" s="67"/>
+      <c r="J7" s="67"/>
+      <c r="K7" s="67"/>
+      <c r="L7" s="67"/>
+      <c r="M7" s="67"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="64">
+      <c r="A8" s="67">
         <v>302.5</v>
       </c>
-      <c r="B8" s="63" t="s">
+      <c r="B8" s="66" t="s">
         <v>80</v>
       </c>
-      <c r="C8" s="63" t="s">
+      <c r="C8" s="66" t="s">
         <v>81</v>
       </c>
-      <c r="D8" s="64"/>
-      <c r="E8" s="64"/>
-      <c r="F8" s="64"/>
-      <c r="G8" s="67"/>
-      <c r="H8" s="64"/>
-      <c r="I8" s="64" t="s">
-        <v>73</v>
-      </c>
-      <c r="J8" s="64"/>
-      <c r="K8" s="64"/>
-      <c r="L8" s="64"/>
-      <c r="M8" s="64"/>
+      <c r="D8" s="67"/>
+      <c r="E8" s="67"/>
+      <c r="F8" s="67"/>
+      <c r="G8" s="70"/>
+      <c r="H8" s="67"/>
+      <c r="I8" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="J8" s="67"/>
+      <c r="K8" s="67"/>
+      <c r="L8" s="67"/>
+      <c r="M8" s="67"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="64">
+      <c r="A9" s="67">
         <v>302.60000000000002</v>
       </c>
-      <c r="B9" s="63" t="s">
+      <c r="B9" s="66" t="s">
         <v>82</v>
       </c>
-      <c r="C9" s="63" t="s">
+      <c r="C9" s="66" t="s">
         <v>83</v>
       </c>
-      <c r="D9" s="64"/>
-      <c r="E9" s="64"/>
-      <c r="F9" s="64"/>
-      <c r="G9" s="67"/>
-      <c r="H9" s="64"/>
-      <c r="I9" s="64"/>
-      <c r="J9" s="64" t="s">
-        <v>73</v>
-      </c>
-      <c r="K9" s="64"/>
-      <c r="L9" s="64"/>
-      <c r="M9" s="64"/>
+      <c r="D9" s="67"/>
+      <c r="E9" s="67"/>
+      <c r="F9" s="67"/>
+      <c r="G9" s="70"/>
+      <c r="H9" s="67"/>
+      <c r="I9" s="67"/>
+      <c r="J9" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="K9" s="67"/>
+      <c r="L9" s="67"/>
+      <c r="M9" s="67"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="64">
+      <c r="A10" s="67">
         <v>302.7</v>
       </c>
-      <c r="B10" s="63" t="s">
+      <c r="B10" s="66" t="s">
         <v>84</v>
       </c>
-      <c r="C10" s="63" t="s">
+      <c r="C10" s="66" t="s">
         <v>85</v>
       </c>
-      <c r="D10" s="64"/>
-      <c r="E10" s="64"/>
-      <c r="F10" s="64"/>
-      <c r="G10" s="67"/>
-      <c r="H10" s="64"/>
-      <c r="I10" s="64"/>
-      <c r="J10" s="64"/>
-      <c r="K10" s="64" t="s">
-        <v>73</v>
-      </c>
-      <c r="L10" s="64" t="s">
-        <v>73</v>
-      </c>
-      <c r="M10" s="64"/>
+      <c r="D10" s="67"/>
+      <c r="E10" s="67"/>
+      <c r="F10" s="67"/>
+      <c r="G10" s="70"/>
+      <c r="H10" s="67"/>
+      <c r="I10" s="67"/>
+      <c r="J10" s="67"/>
+      <c r="K10" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="L10" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="M10" s="67"/>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="64">
+      <c r="A11" s="67">
         <v>302.8</v>
       </c>
-      <c r="B11" s="63" t="s">
+      <c r="B11" s="66" t="s">
         <v>86</v>
       </c>
-      <c r="C11" s="63" t="s">
+      <c r="C11" s="66" t="s">
         <v>87</v>
       </c>
-      <c r="D11" s="64"/>
-      <c r="E11" s="64"/>
-      <c r="F11" s="64"/>
-      <c r="G11" s="67"/>
-      <c r="H11" s="64"/>
-      <c r="I11" s="64"/>
-      <c r="J11" s="64"/>
-      <c r="K11" s="64" t="s">
+      <c r="D11" s="67"/>
+      <c r="E11" s="67"/>
+      <c r="F11" s="67"/>
+      <c r="G11" s="70"/>
+      <c r="H11" s="67"/>
+      <c r="I11" s="67"/>
+      <c r="J11" s="67"/>
+      <c r="K11" s="67" t="s">
         <v>68</v>
       </c>
-      <c r="L11" s="64" t="s">
-        <v>73</v>
-      </c>
-      <c r="M11" s="64"/>
+      <c r="L11" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="M11" s="67"/>
     </row>
     <row r="12" spans="1:13" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="64">
+      <c r="A12" s="67">
         <v>302.89999999999998</v>
       </c>
-      <c r="B12" s="63" t="s">
+      <c r="B12" s="66" t="s">
         <v>88</v>
       </c>
-      <c r="C12" s="63" t="s">
+      <c r="C12" s="66" t="s">
         <v>89</v>
       </c>
-      <c r="D12" s="64"/>
-      <c r="E12" s="64"/>
-      <c r="F12" s="64"/>
-      <c r="G12" s="67"/>
-      <c r="H12" s="64"/>
-      <c r="I12" s="64"/>
-      <c r="J12" s="64"/>
-      <c r="K12" s="64"/>
-      <c r="L12" s="64"/>
-      <c r="M12" s="64"/>
+      <c r="D12" s="67"/>
+      <c r="E12" s="67"/>
+      <c r="F12" s="67"/>
+      <c r="G12" s="70"/>
+      <c r="H12" s="67"/>
+      <c r="I12" s="67"/>
+      <c r="J12" s="67"/>
+      <c r="K12" s="67"/>
+      <c r="L12" s="67"/>
+      <c r="M12" s="67"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="64">
+      <c r="A13" s="67">
         <v>402</v>
       </c>
-      <c r="B13" s="63" t="s">
+      <c r="B13" s="66" t="s">
         <v>90</v>
       </c>
-      <c r="C13" s="63" t="s">
+      <c r="C13" s="66" t="s">
         <v>91</v>
       </c>
-      <c r="D13" s="64"/>
-      <c r="E13" s="65" t="s">
-        <v>73</v>
-      </c>
-      <c r="F13" s="65" t="s">
-        <v>73</v>
-      </c>
-      <c r="G13" s="66"/>
-      <c r="H13" s="65"/>
-      <c r="I13" s="65"/>
-      <c r="J13" s="65"/>
-      <c r="K13" s="65"/>
-      <c r="L13" s="65"/>
-      <c r="M13" s="65"/>
-    </row>
-    <row r="14" spans="1:13" s="71" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="68">
+      <c r="D13" s="67"/>
+      <c r="E13" s="68" t="s">
+        <v>73</v>
+      </c>
+      <c r="F13" s="68" t="s">
+        <v>73</v>
+      </c>
+      <c r="G13" s="69"/>
+      <c r="H13" s="68"/>
+      <c r="I13" s="68"/>
+      <c r="J13" s="68"/>
+      <c r="K13" s="68"/>
+      <c r="L13" s="68"/>
+      <c r="M13" s="68"/>
+    </row>
+    <row r="14" spans="1:13" s="74" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="71">
         <v>402.1</v>
       </c>
-      <c r="B14" s="69" t="s">
+      <c r="B14" s="72" t="s">
         <v>66</v>
       </c>
-      <c r="C14" s="69" t="s">
+      <c r="C14" s="72" t="s">
         <v>67</v>
       </c>
-      <c r="D14" s="70"/>
-      <c r="E14" s="65"/>
-      <c r="F14" s="65"/>
-      <c r="G14" s="66"/>
-      <c r="H14" s="65"/>
-      <c r="I14" s="65"/>
-      <c r="J14" s="65"/>
-      <c r="K14" s="65"/>
-      <c r="L14" s="65"/>
-      <c r="M14" s="65"/>
+      <c r="D14" s="73"/>
+      <c r="E14" s="68"/>
+      <c r="F14" s="68"/>
+      <c r="G14" s="69"/>
+      <c r="H14" s="68"/>
+      <c r="I14" s="68"/>
+      <c r="J14" s="68"/>
+      <c r="K14" s="68"/>
+      <c r="L14" s="68"/>
+      <c r="M14" s="68"/>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="64">
+      <c r="A15" s="67">
         <v>402.2</v>
       </c>
-      <c r="B15" s="63" t="s">
+      <c r="B15" s="66" t="s">
         <v>92</v>
       </c>
-      <c r="C15" s="63" t="s">
+      <c r="C15" s="66" t="s">
         <v>93</v>
       </c>
-      <c r="D15" s="64"/>
-      <c r="E15" s="65"/>
-      <c r="F15" s="65"/>
-      <c r="G15" s="66"/>
-      <c r="H15" s="65"/>
-      <c r="I15" s="65"/>
-      <c r="J15" s="65"/>
-      <c r="K15" s="65"/>
-      <c r="L15" s="65"/>
-      <c r="M15" s="65"/>
+      <c r="D15" s="67"/>
+      <c r="E15" s="68"/>
+      <c r="F15" s="68"/>
+      <c r="G15" s="69"/>
+      <c r="H15" s="68"/>
+      <c r="I15" s="68"/>
+      <c r="J15" s="68"/>
+      <c r="K15" s="68"/>
+      <c r="L15" s="68"/>
+      <c r="M15" s="68"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="64" t="s">
+      <c r="A16" s="67" t="s">
         <v>94</v>
       </c>
-      <c r="B16" s="63" t="s">
+      <c r="B16" s="66" t="s">
         <v>95</v>
       </c>
-      <c r="C16" s="63" t="s">
+      <c r="C16" s="66" t="s">
         <v>96</v>
       </c>
-      <c r="D16" s="64"/>
-      <c r="E16" s="64" t="s">
-        <v>73</v>
-      </c>
-      <c r="F16" s="64"/>
-      <c r="G16" s="67"/>
-      <c r="H16" s="64"/>
-      <c r="I16" s="64"/>
-      <c r="J16" s="64"/>
-      <c r="K16" s="64"/>
-      <c r="L16" s="64"/>
-      <c r="M16" s="64"/>
+      <c r="D16" s="67"/>
+      <c r="E16" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="F16" s="67"/>
+      <c r="G16" s="70"/>
+      <c r="H16" s="67"/>
+      <c r="I16" s="67"/>
+      <c r="J16" s="67"/>
+      <c r="K16" s="67"/>
+      <c r="L16" s="67"/>
+      <c r="M16" s="67"/>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="64" t="s">
+      <c r="A17" s="67" t="s">
         <v>97</v>
       </c>
-      <c r="B17" s="63" t="s">
+      <c r="B17" s="66" t="s">
         <v>98</v>
       </c>
-      <c r="C17" s="63" t="s">
+      <c r="C17" s="66" t="s">
         <v>99</v>
       </c>
-      <c r="D17" s="64"/>
-      <c r="E17" s="64" t="s">
-        <v>73</v>
-      </c>
-      <c r="F17" s="64"/>
-      <c r="G17" s="67"/>
-      <c r="H17" s="64"/>
-      <c r="I17" s="64"/>
-      <c r="J17" s="64"/>
-      <c r="K17" s="64"/>
-      <c r="L17" s="64"/>
-      <c r="M17" s="64"/>
+      <c r="D17" s="67"/>
+      <c r="E17" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="F17" s="67"/>
+      <c r="G17" s="70"/>
+      <c r="H17" s="67"/>
+      <c r="I17" s="67"/>
+      <c r="J17" s="67"/>
+      <c r="K17" s="67"/>
+      <c r="L17" s="67"/>
+      <c r="M17" s="67"/>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="64" t="s">
+      <c r="A18" s="67" t="s">
         <v>100</v>
       </c>
-      <c r="B18" s="63" t="s">
+      <c r="B18" s="66" t="s">
         <v>101</v>
       </c>
-      <c r="C18" s="63" t="s">
+      <c r="C18" s="66" t="s">
         <v>102</v>
       </c>
-      <c r="D18" s="64"/>
-      <c r="E18" s="64" t="s">
-        <v>73</v>
-      </c>
-      <c r="F18" s="64" t="s">
-        <v>73</v>
-      </c>
-      <c r="G18" s="67"/>
-      <c r="H18" s="64"/>
-      <c r="I18" s="64"/>
-      <c r="J18" s="64"/>
-      <c r="K18" s="64"/>
-      <c r="L18" s="64"/>
-      <c r="M18" s="64"/>
+      <c r="D18" s="67"/>
+      <c r="E18" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="F18" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="G18" s="70"/>
+      <c r="H18" s="67"/>
+      <c r="I18" s="67"/>
+      <c r="J18" s="67"/>
+      <c r="K18" s="67"/>
+      <c r="L18" s="67"/>
+      <c r="M18" s="67"/>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="64" t="s">
+      <c r="A19" s="67" t="s">
         <v>103</v>
       </c>
-      <c r="B19" s="63" t="s">
+      <c r="B19" s="66" t="s">
         <v>104</v>
       </c>
-      <c r="C19" s="63" t="s">
+      <c r="C19" s="66" t="s">
         <v>105</v>
       </c>
-      <c r="D19" s="64"/>
-      <c r="E19" s="64" t="s">
-        <v>73</v>
-      </c>
-      <c r="F19" s="64" t="s">
-        <v>73</v>
-      </c>
-      <c r="G19" s="67"/>
-      <c r="H19" s="64"/>
-      <c r="I19" s="64"/>
-      <c r="J19" s="64"/>
-      <c r="K19" s="64"/>
-      <c r="L19" s="64"/>
-      <c r="M19" s="64"/>
+      <c r="D19" s="67"/>
+      <c r="E19" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="F19" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="G19" s="70"/>
+      <c r="H19" s="67"/>
+      <c r="I19" s="67"/>
+      <c r="J19" s="67"/>
+      <c r="K19" s="67"/>
+      <c r="L19" s="67"/>
+      <c r="M19" s="67"/>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="64" t="s">
+      <c r="A20" s="67" t="s">
         <v>106</v>
       </c>
-      <c r="B20" s="63" t="s">
+      <c r="B20" s="66" t="s">
         <v>107</v>
       </c>
-      <c r="C20" s="63" t="s">
+      <c r="C20" s="66" t="s">
         <v>108</v>
       </c>
-      <c r="D20" s="64"/>
-      <c r="E20" s="64" t="s">
-        <v>73</v>
-      </c>
-      <c r="F20" s="64"/>
-      <c r="G20" s="67"/>
-      <c r="H20" s="64"/>
-      <c r="I20" s="64"/>
-      <c r="J20" s="64"/>
-      <c r="K20" s="64"/>
-      <c r="L20" s="64"/>
-      <c r="M20" s="64"/>
+      <c r="D20" s="67"/>
+      <c r="E20" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="F20" s="67"/>
+      <c r="G20" s="70"/>
+      <c r="H20" s="67"/>
+      <c r="I20" s="67"/>
+      <c r="J20" s="67"/>
+      <c r="K20" s="67"/>
+      <c r="L20" s="67"/>
+      <c r="M20" s="67"/>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="64">
+      <c r="A21" s="67">
         <v>402.3</v>
       </c>
-      <c r="B21" s="63" t="s">
+      <c r="B21" s="66" t="s">
         <v>109</v>
       </c>
-      <c r="C21" s="63" t="s">
+      <c r="C21" s="66" t="s">
         <v>110</v>
       </c>
-      <c r="D21" s="64"/>
-      <c r="E21" s="64"/>
-      <c r="F21" s="64"/>
-      <c r="G21" s="67"/>
-      <c r="H21" s="64"/>
-      <c r="I21" s="64" t="s">
-        <v>73</v>
-      </c>
-      <c r="J21" s="64"/>
-      <c r="K21" s="64"/>
-      <c r="L21" s="64"/>
-      <c r="M21" s="64"/>
+      <c r="D21" s="67"/>
+      <c r="E21" s="67"/>
+      <c r="F21" s="67"/>
+      <c r="G21" s="70"/>
+      <c r="H21" s="67"/>
+      <c r="I21" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="J21" s="67"/>
+      <c r="K21" s="67"/>
+      <c r="L21" s="67"/>
+      <c r="M21" s="67"/>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="64" t="s">
+      <c r="A22" s="67" t="s">
         <v>111</v>
       </c>
-      <c r="B22" s="63" t="s">
+      <c r="B22" s="66" t="s">
         <v>112</v>
       </c>
-      <c r="C22" s="63" t="s">
+      <c r="C22" s="66" t="s">
         <v>113</v>
       </c>
-      <c r="D22" s="64"/>
-      <c r="E22" s="64" t="s">
-        <v>73</v>
-      </c>
-      <c r="F22" s="64"/>
-      <c r="G22" s="67"/>
-      <c r="H22" s="64"/>
-      <c r="I22" s="64" t="s">
-        <v>73</v>
-      </c>
-      <c r="J22" s="64"/>
-      <c r="K22" s="64"/>
-      <c r="L22" s="64"/>
-      <c r="M22" s="64"/>
+      <c r="D22" s="67"/>
+      <c r="E22" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="F22" s="67"/>
+      <c r="G22" s="70"/>
+      <c r="H22" s="67"/>
+      <c r="I22" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="J22" s="67"/>
+      <c r="K22" s="67"/>
+      <c r="L22" s="67"/>
+      <c r="M22" s="67"/>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="64" t="s">
+      <c r="A23" s="67" t="s">
         <v>114</v>
       </c>
-      <c r="B23" s="63" t="s">
+      <c r="B23" s="66" t="s">
         <v>115</v>
       </c>
-      <c r="C23" s="63" t="s">
+      <c r="C23" s="66" t="s">
         <v>116</v>
       </c>
-      <c r="D23" s="64"/>
-      <c r="E23" s="64" t="s">
-        <v>73</v>
-      </c>
-      <c r="F23" s="64"/>
-      <c r="G23" s="67"/>
-      <c r="H23" s="64"/>
-      <c r="I23" s="64" t="s">
-        <v>73</v>
-      </c>
-      <c r="J23" s="64"/>
-      <c r="K23" s="64"/>
-      <c r="L23" s="64"/>
-      <c r="M23" s="64"/>
+      <c r="D23" s="67"/>
+      <c r="E23" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="F23" s="67"/>
+      <c r="G23" s="70"/>
+      <c r="H23" s="67"/>
+      <c r="I23" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="J23" s="67"/>
+      <c r="K23" s="67"/>
+      <c r="L23" s="67"/>
+      <c r="M23" s="67"/>
     </row>
     <row r="24" spans="1:13" ht="22" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="64">
+      <c r="A24" s="67">
         <v>402.4</v>
       </c>
-      <c r="B24" s="63" t="s">
+      <c r="B24" s="66" t="s">
         <v>117</v>
       </c>
-      <c r="C24" s="63" t="s">
+      <c r="C24" s="66" t="s">
         <v>118</v>
       </c>
-      <c r="D24" s="64"/>
-      <c r="E24" s="64"/>
-      <c r="F24" s="64" t="s">
-        <v>73</v>
-      </c>
-      <c r="G24" s="67"/>
-      <c r="H24" s="64"/>
-      <c r="I24" s="64"/>
-      <c r="J24" s="64"/>
-      <c r="K24" s="64"/>
-      <c r="L24" s="64"/>
-      <c r="M24" s="64"/>
+      <c r="D24" s="67"/>
+      <c r="E24" s="67"/>
+      <c r="F24" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="G24" s="70"/>
+      <c r="H24" s="67"/>
+      <c r="I24" s="67"/>
+      <c r="J24" s="67"/>
+      <c r="K24" s="67"/>
+      <c r="L24" s="67"/>
+      <c r="M24" s="67"/>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="64">
+      <c r="A25" s="67">
         <v>402.5</v>
       </c>
-      <c r="B25" s="63" t="s">
+      <c r="B25" s="66" t="s">
         <v>119</v>
       </c>
-      <c r="C25" s="63" t="s">
+      <c r="C25" s="66" t="s">
         <v>120</v>
       </c>
-      <c r="D25" s="64"/>
-      <c r="E25" s="64"/>
-      <c r="F25" s="64" t="s">
-        <v>73</v>
-      </c>
-      <c r="G25" s="67"/>
-      <c r="H25" s="64"/>
-      <c r="I25" s="64"/>
-      <c r="J25" s="64"/>
-      <c r="K25" s="64"/>
-      <c r="L25" s="64"/>
-      <c r="M25" s="64"/>
+      <c r="D25" s="67"/>
+      <c r="E25" s="67"/>
+      <c r="F25" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="G25" s="70"/>
+      <c r="H25" s="67"/>
+      <c r="I25" s="67"/>
+      <c r="J25" s="67"/>
+      <c r="K25" s="67"/>
+      <c r="L25" s="67"/>
+      <c r="M25" s="67"/>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="64">
+      <c r="A26" s="67">
         <v>403</v>
       </c>
-      <c r="B26" s="63" t="s">
+      <c r="B26" s="66" t="s">
         <v>121</v>
       </c>
-      <c r="C26" s="63" t="s">
+      <c r="C26" s="66" t="s">
         <v>122</v>
       </c>
-      <c r="D26" s="64"/>
-      <c r="E26" s="65"/>
-      <c r="F26" s="65" t="s">
-        <v>73</v>
-      </c>
-      <c r="G26" s="66"/>
-      <c r="H26" s="65"/>
-      <c r="I26" s="65"/>
-      <c r="J26" s="65" t="s">
-        <v>73</v>
-      </c>
-      <c r="K26" s="65" t="s">
-        <v>73</v>
-      </c>
-      <c r="L26" s="65" t="s">
-        <v>73</v>
-      </c>
-      <c r="M26" s="65"/>
+      <c r="D26" s="67"/>
+      <c r="E26" s="68"/>
+      <c r="F26" s="68" t="s">
+        <v>73</v>
+      </c>
+      <c r="G26" s="69"/>
+      <c r="H26" s="68"/>
+      <c r="I26" s="68"/>
+      <c r="J26" s="68" t="s">
+        <v>73</v>
+      </c>
+      <c r="K26" s="68" t="s">
+        <v>73</v>
+      </c>
+      <c r="L26" s="68" t="s">
+        <v>73</v>
+      </c>
+      <c r="M26" s="68"/>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" s="64">
+      <c r="A27" s="67">
         <v>403.1</v>
       </c>
-      <c r="B27" s="63" t="s">
+      <c r="B27" s="66" t="s">
         <v>123</v>
       </c>
-      <c r="C27" s="63" t="s">
+      <c r="C27" s="66" t="s">
         <v>124</v>
       </c>
-      <c r="D27" s="64"/>
-      <c r="E27" s="65"/>
-      <c r="F27" s="65"/>
-      <c r="G27" s="66"/>
-      <c r="H27" s="65"/>
-      <c r="I27" s="65"/>
-      <c r="J27" s="65"/>
-      <c r="K27" s="65"/>
-      <c r="L27" s="65"/>
-      <c r="M27" s="65"/>
+      <c r="D27" s="67"/>
+      <c r="E27" s="68"/>
+      <c r="F27" s="68"/>
+      <c r="G27" s="69"/>
+      <c r="H27" s="68"/>
+      <c r="I27" s="68"/>
+      <c r="J27" s="68"/>
+      <c r="K27" s="68"/>
+      <c r="L27" s="68"/>
+      <c r="M27" s="68"/>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" s="64">
+      <c r="A28" s="67">
         <v>404</v>
       </c>
-      <c r="B28" s="63" t="s">
+      <c r="B28" s="66" t="s">
         <v>125</v>
       </c>
-      <c r="C28" s="63" t="s">
+      <c r="C28" s="66" t="s">
         <v>126</v>
       </c>
-      <c r="D28" s="64"/>
-      <c r="E28" s="65" t="s">
-        <v>73</v>
-      </c>
-      <c r="F28" s="65"/>
-      <c r="G28" s="66"/>
-      <c r="H28" s="65" t="s">
-        <v>73</v>
-      </c>
-      <c r="I28" s="65" t="s">
-        <v>73</v>
-      </c>
-      <c r="J28" s="65"/>
-      <c r="K28" s="65" t="s">
-        <v>73</v>
-      </c>
-      <c r="L28" s="65" t="s">
-        <v>73</v>
-      </c>
-      <c r="M28" s="65"/>
+      <c r="D28" s="67"/>
+      <c r="E28" s="68" t="s">
+        <v>73</v>
+      </c>
+      <c r="F28" s="68"/>
+      <c r="G28" s="69"/>
+      <c r="H28" s="68" t="s">
+        <v>73</v>
+      </c>
+      <c r="I28" s="68" t="s">
+        <v>73</v>
+      </c>
+      <c r="J28" s="68"/>
+      <c r="K28" s="68" t="s">
+        <v>73</v>
+      </c>
+      <c r="L28" s="68" t="s">
+        <v>73</v>
+      </c>
+      <c r="M28" s="68"/>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="64">
+      <c r="A29" s="67">
         <v>404.1</v>
       </c>
-      <c r="B29" s="63" t="s">
+      <c r="B29" s="66" t="s">
         <v>123</v>
       </c>
-      <c r="C29" s="63" t="s">
+      <c r="C29" s="66" t="s">
         <v>127</v>
       </c>
-      <c r="D29" s="64"/>
-      <c r="E29" s="65"/>
-      <c r="F29" s="65"/>
-      <c r="G29" s="66"/>
-      <c r="H29" s="65"/>
-      <c r="I29" s="65"/>
-      <c r="J29" s="65"/>
-      <c r="K29" s="65"/>
-      <c r="L29" s="65"/>
-      <c r="M29" s="65"/>
+      <c r="D29" s="67"/>
+      <c r="E29" s="68"/>
+      <c r="F29" s="68"/>
+      <c r="G29" s="69"/>
+      <c r="H29" s="68"/>
+      <c r="I29" s="68"/>
+      <c r="J29" s="68"/>
+      <c r="K29" s="68"/>
+      <c r="L29" s="68"/>
+      <c r="M29" s="68"/>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="64">
+      <c r="A30" s="67">
         <v>405</v>
       </c>
-      <c r="B30" s="63" t="s">
+      <c r="B30" s="66" t="s">
         <v>128</v>
       </c>
-      <c r="C30" s="63" t="s">
+      <c r="C30" s="66" t="s">
         <v>129</v>
       </c>
-      <c r="D30" s="64"/>
-      <c r="E30" s="65" t="s">
-        <v>73</v>
-      </c>
-      <c r="F30" s="65" t="s">
-        <v>73</v>
-      </c>
-      <c r="G30" s="66"/>
-      <c r="H30" s="65"/>
-      <c r="I30" s="65"/>
-      <c r="J30" s="65"/>
-      <c r="K30" s="65"/>
-      <c r="L30" s="65"/>
-      <c r="M30" s="65"/>
+      <c r="D30" s="67"/>
+      <c r="E30" s="68" t="s">
+        <v>73</v>
+      </c>
+      <c r="F30" s="68" t="s">
+        <v>73</v>
+      </c>
+      <c r="G30" s="69"/>
+      <c r="H30" s="68"/>
+      <c r="I30" s="68"/>
+      <c r="J30" s="68"/>
+      <c r="K30" s="68"/>
+      <c r="L30" s="68"/>
+      <c r="M30" s="68"/>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="64">
+      <c r="A31" s="67">
         <v>405.1</v>
       </c>
-      <c r="B31" s="63" t="s">
+      <c r="B31" s="66" t="s">
         <v>123</v>
       </c>
-      <c r="C31" s="63" t="s">
+      <c r="C31" s="66" t="s">
         <v>124</v>
       </c>
-      <c r="D31" s="64"/>
-      <c r="E31" s="65"/>
-      <c r="F31" s="65"/>
-      <c r="G31" s="66"/>
-      <c r="H31" s="65"/>
-      <c r="I31" s="65"/>
-      <c r="J31" s="65"/>
-      <c r="K31" s="65"/>
-      <c r="L31" s="65"/>
-      <c r="M31" s="65"/>
+      <c r="D31" s="67"/>
+      <c r="E31" s="68"/>
+      <c r="F31" s="68"/>
+      <c r="G31" s="69"/>
+      <c r="H31" s="68"/>
+      <c r="I31" s="68"/>
+      <c r="J31" s="68"/>
+      <c r="K31" s="68"/>
+      <c r="L31" s="68"/>
+      <c r="M31" s="68"/>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="64">
+      <c r="A32" s="67">
         <v>406</v>
       </c>
-      <c r="B32" s="63" t="s">
+      <c r="B32" s="66" t="s">
         <v>130</v>
       </c>
-      <c r="C32" s="63" t="s">
+      <c r="C32" s="66" t="s">
         <v>131</v>
       </c>
-      <c r="D32" s="64"/>
-      <c r="E32" s="65" t="s">
-        <v>73</v>
-      </c>
-      <c r="F32" s="65"/>
-      <c r="G32" s="66"/>
-      <c r="H32" s="65"/>
-      <c r="I32" s="65" t="s">
-        <v>73</v>
-      </c>
-      <c r="J32" s="65"/>
-      <c r="K32" s="65" t="s">
-        <v>73</v>
-      </c>
-      <c r="L32" s="65" t="s">
-        <v>73</v>
-      </c>
-      <c r="M32" s="65" t="s">
+      <c r="D32" s="67"/>
+      <c r="E32" s="68" t="s">
+        <v>73</v>
+      </c>
+      <c r="F32" s="68"/>
+      <c r="G32" s="69"/>
+      <c r="H32" s="68"/>
+      <c r="I32" s="68" t="s">
+        <v>73</v>
+      </c>
+      <c r="J32" s="68"/>
+      <c r="K32" s="68" t="s">
+        <v>73</v>
+      </c>
+      <c r="L32" s="68" t="s">
+        <v>73</v>
+      </c>
+      <c r="M32" s="68" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="64">
+      <c r="A33" s="67">
         <v>406.1</v>
       </c>
-      <c r="B33" s="63" t="s">
+      <c r="B33" s="66" t="s">
         <v>123</v>
       </c>
-      <c r="C33" s="63" t="s">
+      <c r="C33" s="66" t="s">
         <v>124</v>
       </c>
-      <c r="D33" s="64"/>
-      <c r="E33" s="65"/>
-      <c r="F33" s="65"/>
-      <c r="G33" s="66"/>
-      <c r="H33" s="65"/>
-      <c r="I33" s="65"/>
-      <c r="J33" s="65"/>
-      <c r="K33" s="65"/>
-      <c r="L33" s="65"/>
-      <c r="M33" s="65"/>
+      <c r="D33" s="67"/>
+      <c r="E33" s="68"/>
+      <c r="F33" s="68"/>
+      <c r="G33" s="69"/>
+      <c r="H33" s="68"/>
+      <c r="I33" s="68"/>
+      <c r="J33" s="68"/>
+      <c r="K33" s="68"/>
+      <c r="L33" s="68"/>
+      <c r="M33" s="68"/>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="64">
+      <c r="A34" s="67">
         <v>407</v>
       </c>
-      <c r="B34" s="63" t="s">
+      <c r="B34" s="66" t="s">
         <v>132</v>
       </c>
-      <c r="C34" s="63" t="s">
+      <c r="C34" s="66" t="s">
         <v>133</v>
       </c>
-      <c r="D34" s="64"/>
-      <c r="E34" s="65" t="s">
-        <v>73</v>
-      </c>
-      <c r="F34" s="65" t="s">
-        <v>73</v>
-      </c>
-      <c r="G34" s="66"/>
-      <c r="H34" s="65" t="s">
-        <v>73</v>
-      </c>
-      <c r="I34" s="65" t="s">
-        <v>73</v>
-      </c>
-      <c r="J34" s="65"/>
-      <c r="K34" s="65" t="s">
-        <v>73</v>
-      </c>
-      <c r="L34" s="65" t="s">
-        <v>73</v>
-      </c>
-      <c r="M34" s="65"/>
+      <c r="D34" s="67"/>
+      <c r="E34" s="68" t="s">
+        <v>73</v>
+      </c>
+      <c r="F34" s="68" t="s">
+        <v>73</v>
+      </c>
+      <c r="G34" s="69"/>
+      <c r="H34" s="68" t="s">
+        <v>73</v>
+      </c>
+      <c r="I34" s="68" t="s">
+        <v>73</v>
+      </c>
+      <c r="J34" s="68"/>
+      <c r="K34" s="68" t="s">
+        <v>73</v>
+      </c>
+      <c r="L34" s="68" t="s">
+        <v>73</v>
+      </c>
+      <c r="M34" s="68"/>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" s="64">
+      <c r="A35" s="67">
         <v>407.1</v>
       </c>
-      <c r="B35" s="63" t="s">
+      <c r="B35" s="66" t="s">
         <v>123</v>
       </c>
-      <c r="C35" s="63" t="s">
+      <c r="C35" s="66" t="s">
         <v>127</v>
       </c>
-      <c r="D35" s="64"/>
-      <c r="E35" s="65"/>
-      <c r="F35" s="65"/>
-      <c r="G35" s="66"/>
-      <c r="H35" s="65"/>
-      <c r="I35" s="65"/>
-      <c r="J35" s="65"/>
-      <c r="K35" s="65"/>
-      <c r="L35" s="65"/>
-      <c r="M35" s="65"/>
+      <c r="D35" s="67"/>
+      <c r="E35" s="68"/>
+      <c r="F35" s="68"/>
+      <c r="G35" s="69"/>
+      <c r="H35" s="68"/>
+      <c r="I35" s="68"/>
+      <c r="J35" s="68"/>
+      <c r="K35" s="68"/>
+      <c r="L35" s="68"/>
+      <c r="M35" s="68"/>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="64">
+      <c r="A36" s="67">
         <v>407.2</v>
       </c>
-      <c r="B36" s="63" t="s">
+      <c r="B36" s="66" t="s">
         <v>134</v>
       </c>
-      <c r="C36" s="63" t="s">
+      <c r="C36" s="66" t="s">
         <v>135</v>
       </c>
-      <c r="D36" s="64"/>
-      <c r="E36" s="64"/>
-      <c r="F36" s="64" t="s">
-        <v>73</v>
-      </c>
-      <c r="G36" s="67"/>
-      <c r="H36" s="64"/>
-      <c r="I36" s="64"/>
-      <c r="J36" s="64"/>
-      <c r="K36" s="64"/>
-      <c r="L36" s="64"/>
-      <c r="M36" s="64"/>
+      <c r="D36" s="67"/>
+      <c r="E36" s="67"/>
+      <c r="F36" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="G36" s="70"/>
+      <c r="H36" s="67"/>
+      <c r="I36" s="67"/>
+      <c r="J36" s="67"/>
+      <c r="K36" s="67"/>
+      <c r="L36" s="67"/>
+      <c r="M36" s="67"/>
     </row>
     <row r="37" spans="1:13" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="64">
+      <c r="A37" s="67">
         <v>407.3</v>
       </c>
-      <c r="B37" s="63" t="s">
+      <c r="B37" s="66" t="s">
         <v>136</v>
       </c>
-      <c r="C37" s="63" t="s">
+      <c r="C37" s="66" t="s">
         <v>137</v>
       </c>
-      <c r="D37" s="64"/>
-      <c r="E37" s="64" t="s">
-        <v>73</v>
-      </c>
-      <c r="F37" s="64"/>
-      <c r="G37" s="67"/>
-      <c r="H37" s="64"/>
-      <c r="I37" s="64"/>
-      <c r="J37" s="64"/>
-      <c r="K37" s="64"/>
-      <c r="L37" s="64"/>
-      <c r="M37" s="64"/>
+      <c r="D37" s="67"/>
+      <c r="E37" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="F37" s="67"/>
+      <c r="G37" s="70"/>
+      <c r="H37" s="67"/>
+      <c r="I37" s="67"/>
+      <c r="J37" s="67"/>
+      <c r="K37" s="67"/>
+      <c r="L37" s="67"/>
+      <c r="M37" s="67"/>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38" s="64">
+      <c r="A38" s="67">
         <v>407.4</v>
       </c>
-      <c r="B38" s="63" t="s">
+      <c r="B38" s="66" t="s">
         <v>138</v>
       </c>
-      <c r="C38" s="63" t="s">
+      <c r="C38" s="66" t="s">
         <v>139</v>
       </c>
-      <c r="D38" s="64"/>
-      <c r="E38" s="64"/>
-      <c r="F38" s="64"/>
-      <c r="G38" s="67"/>
-      <c r="H38" s="64"/>
-      <c r="I38" s="64"/>
-      <c r="J38" s="64"/>
-      <c r="K38" s="64" t="s">
-        <v>73</v>
-      </c>
-      <c r="L38" s="64" t="s">
-        <v>73</v>
-      </c>
-      <c r="M38" s="64"/>
+      <c r="D38" s="67"/>
+      <c r="E38" s="67"/>
+      <c r="F38" s="67"/>
+      <c r="G38" s="70"/>
+      <c r="H38" s="67"/>
+      <c r="I38" s="67"/>
+      <c r="J38" s="67"/>
+      <c r="K38" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="L38" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="M38" s="67"/>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39" s="64">
+      <c r="A39" s="67">
         <v>407.5</v>
       </c>
-      <c r="B39" s="63" t="s">
+      <c r="B39" s="66" t="s">
         <v>140</v>
       </c>
-      <c r="C39" s="63" t="s">
+      <c r="C39" s="66" t="s">
         <v>141</v>
       </c>
-      <c r="D39" s="64"/>
-      <c r="E39" s="64" t="s">
-        <v>73</v>
-      </c>
-      <c r="F39" s="64" t="s">
-        <v>73</v>
-      </c>
-      <c r="G39" s="67"/>
-      <c r="H39" s="64"/>
-      <c r="I39" s="64"/>
-      <c r="J39" s="64"/>
-      <c r="K39" s="64" t="s">
-        <v>73</v>
-      </c>
-      <c r="L39" s="64" t="s">
-        <v>73</v>
-      </c>
-      <c r="M39" s="64"/>
+      <c r="D39" s="67"/>
+      <c r="E39" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="F39" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="G39" s="70"/>
+      <c r="H39" s="67"/>
+      <c r="I39" s="67"/>
+      <c r="J39" s="67"/>
+      <c r="K39" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="L39" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="M39" s="67"/>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" s="64">
+      <c r="A40" s="67">
         <v>407.6</v>
       </c>
-      <c r="B40" s="63" t="s">
+      <c r="B40" s="66" t="s">
         <v>142</v>
       </c>
-      <c r="C40" s="63" t="s">
+      <c r="C40" s="66" t="s">
         <v>143</v>
       </c>
-      <c r="D40" s="64"/>
-      <c r="E40" s="64"/>
-      <c r="F40" s="64"/>
-      <c r="G40" s="67"/>
-      <c r="H40" s="64"/>
-      <c r="I40" s="64"/>
-      <c r="J40" s="64"/>
-      <c r="K40" s="64" t="s">
-        <v>73</v>
-      </c>
-      <c r="L40" s="64" t="s">
-        <v>73</v>
-      </c>
-      <c r="M40" s="64"/>
+      <c r="D40" s="67"/>
+      <c r="E40" s="67"/>
+      <c r="F40" s="67"/>
+      <c r="G40" s="70"/>
+      <c r="H40" s="67"/>
+      <c r="I40" s="67"/>
+      <c r="J40" s="67"/>
+      <c r="K40" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="L40" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="M40" s="67"/>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A41" s="64">
+      <c r="A41" s="67">
         <v>407.7</v>
       </c>
-      <c r="B41" s="63" t="s">
+      <c r="B41" s="66" t="s">
         <v>144</v>
       </c>
-      <c r="C41" s="63" t="s">
+      <c r="C41" s="66" t="s">
         <v>145</v>
       </c>
-      <c r="D41" s="64"/>
-      <c r="E41" s="64" t="s">
-        <v>73</v>
-      </c>
-      <c r="F41" s="64"/>
-      <c r="G41" s="67"/>
-      <c r="H41" s="64"/>
-      <c r="I41" s="64"/>
-      <c r="J41" s="64"/>
-      <c r="K41" s="64"/>
-      <c r="L41" s="64"/>
-      <c r="M41" s="64"/>
+      <c r="D41" s="67"/>
+      <c r="E41" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="F41" s="67"/>
+      <c r="G41" s="70"/>
+      <c r="H41" s="67"/>
+      <c r="I41" s="67"/>
+      <c r="J41" s="67"/>
+      <c r="K41" s="67"/>
+      <c r="L41" s="67"/>
+      <c r="M41" s="67"/>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A42" s="64">
+      <c r="A42" s="67">
         <v>407.8</v>
       </c>
-      <c r="B42" s="63" t="s">
+      <c r="B42" s="66" t="s">
         <v>146</v>
       </c>
-      <c r="C42" s="63" t="s">
+      <c r="C42" s="66" t="s">
         <v>147</v>
       </c>
-      <c r="D42" s="64"/>
-      <c r="E42" s="64"/>
-      <c r="F42" s="64"/>
-      <c r="G42" s="67"/>
-      <c r="H42" s="64"/>
-      <c r="I42" s="64"/>
-      <c r="J42" s="64"/>
-      <c r="K42" s="64" t="s">
-        <v>73</v>
-      </c>
-      <c r="L42" s="64" t="s">
-        <v>73</v>
-      </c>
-      <c r="M42" s="64"/>
+      <c r="D42" s="67"/>
+      <c r="E42" s="67"/>
+      <c r="F42" s="67"/>
+      <c r="G42" s="70"/>
+      <c r="H42" s="67"/>
+      <c r="I42" s="67"/>
+      <c r="J42" s="67"/>
+      <c r="K42" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="L42" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="M42" s="67"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A43" s="64">
+      <c r="A43" s="67">
         <v>408</v>
       </c>
-      <c r="B43" s="63" t="s">
+      <c r="B43" s="66" t="s">
         <v>148</v>
       </c>
-      <c r="C43" s="63" t="s">
+      <c r="C43" s="66" t="s">
         <v>149</v>
       </c>
-      <c r="D43" s="65"/>
-      <c r="E43" s="65"/>
-      <c r="F43" s="65"/>
-      <c r="G43" s="66"/>
-      <c r="H43" s="65"/>
-      <c r="I43" s="65"/>
-      <c r="J43" s="65"/>
-      <c r="K43" s="65" t="s">
-        <v>73</v>
-      </c>
-      <c r="L43" s="65" t="s">
-        <v>73</v>
-      </c>
-      <c r="M43" s="65"/>
+      <c r="D43" s="68"/>
+      <c r="E43" s="68"/>
+      <c r="F43" s="68"/>
+      <c r="G43" s="69"/>
+      <c r="H43" s="68"/>
+      <c r="I43" s="68"/>
+      <c r="J43" s="68"/>
+      <c r="K43" s="68" t="s">
+        <v>73</v>
+      </c>
+      <c r="L43" s="68" t="s">
+        <v>73</v>
+      </c>
+      <c r="M43" s="68"/>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A44" s="64">
+      <c r="A44" s="67">
         <v>408.1</v>
       </c>
-      <c r="B44" s="63" t="s">
+      <c r="B44" s="66" t="s">
         <v>66</v>
       </c>
-      <c r="C44" s="63" t="s">
+      <c r="C44" s="66" t="s">
         <v>124</v>
       </c>
-      <c r="D44" s="65"/>
-      <c r="E44" s="65"/>
-      <c r="F44" s="65"/>
-      <c r="G44" s="66"/>
-      <c r="H44" s="65"/>
-      <c r="I44" s="65"/>
-      <c r="J44" s="65"/>
-      <c r="K44" s="65"/>
-      <c r="L44" s="65"/>
-      <c r="M44" s="65"/>
+      <c r="D44" s="68"/>
+      <c r="E44" s="68"/>
+      <c r="F44" s="68"/>
+      <c r="G44" s="69"/>
+      <c r="H44" s="68"/>
+      <c r="I44" s="68"/>
+      <c r="J44" s="68"/>
+      <c r="K44" s="68"/>
+      <c r="L44" s="68"/>
+      <c r="M44" s="68"/>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A45" s="64">
+      <c r="A45" s="67">
         <v>408.2</v>
       </c>
-      <c r="B45" s="63" t="s">
+      <c r="B45" s="66" t="s">
         <v>150</v>
       </c>
-      <c r="C45" s="63" t="s">
+      <c r="C45" s="66" t="s">
         <v>151</v>
       </c>
-      <c r="D45" s="65"/>
-      <c r="E45" s="65"/>
-      <c r="F45" s="65"/>
-      <c r="G45" s="66"/>
-      <c r="H45" s="65"/>
-      <c r="I45" s="65"/>
-      <c r="J45" s="65"/>
-      <c r="K45" s="65"/>
-      <c r="L45" s="65"/>
-      <c r="M45" s="65"/>
+      <c r="D45" s="68"/>
+      <c r="E45" s="68"/>
+      <c r="F45" s="68"/>
+      <c r="G45" s="69"/>
+      <c r="H45" s="68"/>
+      <c r="I45" s="68"/>
+      <c r="J45" s="68"/>
+      <c r="K45" s="68"/>
+      <c r="L45" s="68"/>
+      <c r="M45" s="68"/>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A46" s="64">
+      <c r="A46" s="67">
         <v>408.3</v>
       </c>
-      <c r="B46" s="63" t="s">
+      <c r="B46" s="66" t="s">
         <v>152</v>
       </c>
-      <c r="C46" s="63" t="s">
+      <c r="C46" s="66" t="s">
         <v>153</v>
       </c>
-      <c r="D46" s="64"/>
-      <c r="E46" s="64"/>
-      <c r="F46" s="64"/>
-      <c r="G46" s="67"/>
-      <c r="H46" s="64"/>
-      <c r="I46" s="64"/>
-      <c r="J46" s="64"/>
-      <c r="K46" s="64"/>
-      <c r="L46" s="64"/>
-      <c r="M46" s="64"/>
+      <c r="D46" s="67"/>
+      <c r="E46" s="67"/>
+      <c r="F46" s="67"/>
+      <c r="G46" s="70"/>
+      <c r="H46" s="67"/>
+      <c r="I46" s="67"/>
+      <c r="J46" s="67"/>
+      <c r="K46" s="67"/>
+      <c r="L46" s="67"/>
+      <c r="M46" s="67"/>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A47" s="64">
+      <c r="A47" s="67">
         <v>409</v>
       </c>
-      <c r="B47" s="63" t="s">
+      <c r="B47" s="66" t="s">
         <v>154</v>
       </c>
-      <c r="C47" s="63" t="s">
+      <c r="C47" s="66" t="s">
         <v>155</v>
       </c>
-      <c r="D47" s="64"/>
-      <c r="E47" s="65" t="s">
-        <v>73</v>
-      </c>
-      <c r="F47" s="65"/>
-      <c r="G47" s="66"/>
-      <c r="H47" s="65"/>
-      <c r="I47" s="65"/>
-      <c r="J47" s="65"/>
-      <c r="K47" s="65"/>
-      <c r="L47" s="65"/>
-      <c r="M47" s="65"/>
+      <c r="D47" s="67"/>
+      <c r="E47" s="68" t="s">
+        <v>73</v>
+      </c>
+      <c r="F47" s="68"/>
+      <c r="G47" s="69"/>
+      <c r="H47" s="68"/>
+      <c r="I47" s="68"/>
+      <c r="J47" s="68"/>
+      <c r="K47" s="68"/>
+      <c r="L47" s="68"/>
+      <c r="M47" s="68"/>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A48" s="64">
+      <c r="A48" s="67">
         <v>409.1</v>
       </c>
-      <c r="B48" s="63" t="s">
+      <c r="B48" s="66" t="s">
         <v>66</v>
       </c>
-      <c r="C48" s="63" t="s">
+      <c r="C48" s="66" t="s">
         <v>127</v>
       </c>
-      <c r="D48" s="64"/>
-      <c r="E48" s="65"/>
-      <c r="F48" s="65"/>
-      <c r="G48" s="66"/>
-      <c r="H48" s="65"/>
-      <c r="I48" s="65"/>
-      <c r="J48" s="65"/>
-      <c r="K48" s="65"/>
-      <c r="L48" s="65"/>
-      <c r="M48" s="65"/>
+      <c r="D48" s="67"/>
+      <c r="E48" s="68"/>
+      <c r="F48" s="68"/>
+      <c r="G48" s="69"/>
+      <c r="H48" s="68"/>
+      <c r="I48" s="68"/>
+      <c r="J48" s="68"/>
+      <c r="K48" s="68"/>
+      <c r="L48" s="68"/>
+      <c r="M48" s="68"/>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A49" s="64">
+      <c r="A49" s="67">
         <v>410</v>
       </c>
-      <c r="B49" s="63" t="s">
+      <c r="B49" s="66" t="s">
         <v>156</v>
       </c>
-      <c r="C49" s="63" t="s">
+      <c r="C49" s="66" t="s">
         <v>157</v>
       </c>
-      <c r="D49" s="64"/>
-      <c r="E49" s="65"/>
-      <c r="F49" s="65" t="s">
-        <v>73</v>
-      </c>
-      <c r="G49" s="66"/>
-      <c r="H49" s="65"/>
-      <c r="I49" s="65"/>
-      <c r="J49" s="65"/>
-      <c r="K49" s="65"/>
-      <c r="L49" s="65"/>
-      <c r="M49" s="65"/>
+      <c r="D49" s="67"/>
+      <c r="E49" s="68"/>
+      <c r="F49" s="68" t="s">
+        <v>73</v>
+      </c>
+      <c r="G49" s="69"/>
+      <c r="H49" s="68"/>
+      <c r="I49" s="68"/>
+      <c r="J49" s="68"/>
+      <c r="K49" s="68"/>
+      <c r="L49" s="68"/>
+      <c r="M49" s="68"/>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A50" s="64">
+      <c r="A50" s="67">
         <v>410.1</v>
       </c>
-      <c r="B50" s="63" t="s">
+      <c r="B50" s="66" t="s">
         <v>66</v>
       </c>
-      <c r="C50" s="63" t="s">
+      <c r="C50" s="66" t="s">
         <v>124</v>
       </c>
-      <c r="D50" s="64"/>
-      <c r="E50" s="65"/>
-      <c r="F50" s="65"/>
-      <c r="G50" s="66"/>
-      <c r="H50" s="65"/>
-      <c r="I50" s="65"/>
-      <c r="J50" s="65"/>
-      <c r="K50" s="65"/>
-      <c r="L50" s="65"/>
-      <c r="M50" s="65"/>
+      <c r="D50" s="67"/>
+      <c r="E50" s="68"/>
+      <c r="F50" s="68"/>
+      <c r="G50" s="69"/>
+      <c r="H50" s="68"/>
+      <c r="I50" s="68"/>
+      <c r="J50" s="68"/>
+      <c r="K50" s="68"/>
+      <c r="L50" s="68"/>
+      <c r="M50" s="68"/>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A51" s="64">
+      <c r="A51" s="67">
         <v>411</v>
       </c>
-      <c r="B51" s="63" t="s">
+      <c r="B51" s="66" t="s">
         <v>158</v>
       </c>
-      <c r="C51" s="63" t="s">
+      <c r="C51" s="66" t="s">
         <v>159</v>
       </c>
-      <c r="D51" s="64"/>
-      <c r="E51" s="65"/>
-      <c r="F51" s="65"/>
-      <c r="G51" s="66"/>
-      <c r="H51" s="65" t="s">
-        <v>73</v>
-      </c>
-      <c r="I51" s="65" t="s">
-        <v>73</v>
-      </c>
-      <c r="J51" s="65"/>
-      <c r="K51" s="65"/>
-      <c r="L51" s="65"/>
-      <c r="M51" s="65"/>
+      <c r="D51" s="67"/>
+      <c r="E51" s="68"/>
+      <c r="F51" s="68"/>
+      <c r="G51" s="69"/>
+      <c r="H51" s="68" t="s">
+        <v>73</v>
+      </c>
+      <c r="I51" s="68" t="s">
+        <v>73</v>
+      </c>
+      <c r="J51" s="68"/>
+      <c r="K51" s="68"/>
+      <c r="L51" s="68"/>
+      <c r="M51" s="68"/>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A52" s="64">
+      <c r="A52" s="67">
         <v>411.1</v>
       </c>
-      <c r="B52" s="63" t="s">
+      <c r="B52" s="66" t="s">
         <v>66</v>
       </c>
-      <c r="C52" s="63" t="s">
+      <c r="C52" s="66" t="s">
         <v>124</v>
       </c>
-      <c r="D52" s="64"/>
-      <c r="E52" s="65"/>
-      <c r="F52" s="65"/>
-      <c r="G52" s="66"/>
-      <c r="H52" s="65"/>
-      <c r="I52" s="65"/>
-      <c r="J52" s="65"/>
-      <c r="K52" s="65"/>
-      <c r="L52" s="65"/>
-      <c r="M52" s="65"/>
+      <c r="D52" s="67"/>
+      <c r="E52" s="68"/>
+      <c r="F52" s="68"/>
+      <c r="G52" s="69"/>
+      <c r="H52" s="68"/>
+      <c r="I52" s="68"/>
+      <c r="J52" s="68"/>
+      <c r="K52" s="68"/>
+      <c r="L52" s="68"/>
+      <c r="M52" s="68"/>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A53" s="64">
+      <c r="A53" s="67">
         <v>412</v>
       </c>
-      <c r="B53" s="63" t="s">
+      <c r="B53" s="66" t="s">
         <v>160</v>
       </c>
-      <c r="C53" s="63" t="s">
+      <c r="C53" s="66" t="s">
         <v>161</v>
       </c>
-      <c r="D53" s="64"/>
-      <c r="E53" s="65" t="s">
-        <v>73</v>
-      </c>
-      <c r="F53" s="65"/>
-      <c r="G53" s="66"/>
-      <c r="H53" s="65" t="s">
-        <v>73</v>
-      </c>
-      <c r="I53" s="65" t="s">
-        <v>73</v>
-      </c>
-      <c r="J53" s="65"/>
-      <c r="K53" s="65" t="s">
-        <v>73</v>
-      </c>
-      <c r="L53" s="65" t="s">
-        <v>73</v>
-      </c>
-      <c r="M53" s="65"/>
+      <c r="D53" s="67"/>
+      <c r="E53" s="68" t="s">
+        <v>73</v>
+      </c>
+      <c r="F53" s="68"/>
+      <c r="G53" s="69"/>
+      <c r="H53" s="68" t="s">
+        <v>73</v>
+      </c>
+      <c r="I53" s="68" t="s">
+        <v>73</v>
+      </c>
+      <c r="J53" s="68"/>
+      <c r="K53" s="68" t="s">
+        <v>73</v>
+      </c>
+      <c r="L53" s="68" t="s">
+        <v>73</v>
+      </c>
+      <c r="M53" s="68"/>
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A54" s="64">
+      <c r="A54" s="67">
         <v>412.1</v>
       </c>
-      <c r="B54" s="63" t="s">
+      <c r="B54" s="66" t="s">
         <v>66</v>
       </c>
-      <c r="C54" s="63" t="s">
+      <c r="C54" s="66" t="s">
         <v>124</v>
       </c>
-      <c r="D54" s="64"/>
-      <c r="E54" s="65"/>
-      <c r="F54" s="65"/>
-      <c r="G54" s="66"/>
-      <c r="H54" s="65"/>
-      <c r="I54" s="65"/>
-      <c r="J54" s="65"/>
-      <c r="K54" s="65"/>
-      <c r="L54" s="65"/>
-      <c r="M54" s="65"/>
+      <c r="D54" s="67"/>
+      <c r="E54" s="68"/>
+      <c r="F54" s="68"/>
+      <c r="G54" s="69"/>
+      <c r="H54" s="68"/>
+      <c r="I54" s="68"/>
+      <c r="J54" s="68"/>
+      <c r="K54" s="68"/>
+      <c r="L54" s="68"/>
+      <c r="M54" s="68"/>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A55" s="64">
+      <c r="A55" s="67">
         <v>412.2</v>
       </c>
-      <c r="B55" s="63" t="s">
+      <c r="B55" s="66" t="s">
         <v>162</v>
       </c>
-      <c r="C55" s="63" t="s">
+      <c r="C55" s="66" t="s">
         <v>163</v>
       </c>
-      <c r="D55" s="64"/>
-      <c r="E55" s="64"/>
-      <c r="F55" s="64"/>
-      <c r="G55" s="67"/>
-      <c r="H55" s="64"/>
-      <c r="I55" s="64" t="s">
-        <v>73</v>
-      </c>
-      <c r="J55" s="64"/>
-      <c r="K55" s="64"/>
-      <c r="L55" s="64"/>
-      <c r="M55" s="64"/>
+      <c r="D55" s="67"/>
+      <c r="E55" s="67"/>
+      <c r="F55" s="67"/>
+      <c r="G55" s="70"/>
+      <c r="H55" s="67"/>
+      <c r="I55" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="J55" s="67"/>
+      <c r="K55" s="67"/>
+      <c r="L55" s="67"/>
+      <c r="M55" s="67"/>
     </row>
     <row r="56" spans="1:13" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A56" s="64">
+      <c r="A56" s="67">
         <v>412.3</v>
       </c>
-      <c r="B56" s="63" t="s">
+      <c r="B56" s="66" t="s">
         <v>164</v>
       </c>
-      <c r="C56" s="63" t="s">
+      <c r="C56" s="66" t="s">
         <v>165</v>
       </c>
-      <c r="D56" s="64"/>
-      <c r="E56" s="64"/>
-      <c r="F56" s="64"/>
-      <c r="G56" s="67"/>
-      <c r="H56" s="64"/>
-      <c r="I56" s="64" t="s">
-        <v>73</v>
-      </c>
-      <c r="J56" s="64"/>
-      <c r="K56" s="64"/>
-      <c r="L56" s="64"/>
-      <c r="M56" s="64"/>
+      <c r="D56" s="67"/>
+      <c r="E56" s="67"/>
+      <c r="F56" s="67"/>
+      <c r="G56" s="70"/>
+      <c r="H56" s="67"/>
+      <c r="I56" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="J56" s="67"/>
+      <c r="K56" s="67"/>
+      <c r="L56" s="67"/>
+      <c r="M56" s="67"/>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A57" s="64">
+      <c r="A57" s="67">
         <v>412.4</v>
       </c>
-      <c r="B57" s="63" t="s">
+      <c r="B57" s="66" t="s">
         <v>166</v>
       </c>
-      <c r="C57" s="63" t="s">
+      <c r="C57" s="66" t="s">
         <v>167</v>
       </c>
-      <c r="D57" s="64"/>
-      <c r="E57" s="64"/>
-      <c r="F57" s="64"/>
-      <c r="G57" s="67"/>
-      <c r="H57" s="64"/>
-      <c r="I57" s="64" t="s">
-        <v>73</v>
-      </c>
-      <c r="J57" s="64"/>
-      <c r="K57" s="64"/>
-      <c r="L57" s="64"/>
-      <c r="M57" s="64"/>
+      <c r="D57" s="67"/>
+      <c r="E57" s="67"/>
+      <c r="F57" s="67"/>
+      <c r="G57" s="70"/>
+      <c r="H57" s="67"/>
+      <c r="I57" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="J57" s="67"/>
+      <c r="K57" s="67"/>
+      <c r="L57" s="67"/>
+      <c r="M57" s="67"/>
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A58" s="64">
+      <c r="A58" s="67">
         <v>412.5</v>
       </c>
-      <c r="B58" s="63" t="s">
+      <c r="B58" s="66" t="s">
         <v>168</v>
       </c>
-      <c r="C58" s="63" t="s">
+      <c r="C58" s="66" t="s">
         <v>169</v>
       </c>
-      <c r="D58" s="64"/>
-      <c r="E58" s="64"/>
-      <c r="F58" s="64"/>
-      <c r="G58" s="67"/>
-      <c r="H58" s="64"/>
-      <c r="I58" s="64"/>
-      <c r="J58" s="64"/>
-      <c r="K58" s="64"/>
-      <c r="L58" s="64"/>
-      <c r="M58" s="64"/>
+      <c r="D58" s="67"/>
+      <c r="E58" s="67"/>
+      <c r="F58" s="67"/>
+      <c r="G58" s="70"/>
+      <c r="H58" s="67"/>
+      <c r="I58" s="67"/>
+      <c r="J58" s="67"/>
+      <c r="K58" s="67"/>
+      <c r="L58" s="67"/>
+      <c r="M58" s="67"/>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A59" s="64">
+      <c r="A59" s="67">
         <v>412.6</v>
       </c>
-      <c r="B59" s="63" t="s">
+      <c r="B59" s="66" t="s">
         <v>170</v>
       </c>
-      <c r="C59" s="63" t="s">
+      <c r="C59" s="66" t="s">
         <v>171</v>
       </c>
-      <c r="D59" s="64"/>
-      <c r="E59" s="64" t="s">
-        <v>73</v>
-      </c>
-      <c r="F59" s="64" t="s">
-        <v>73</v>
-      </c>
-      <c r="G59" s="67"/>
-      <c r="H59" s="64" t="s">
-        <v>73</v>
-      </c>
-      <c r="I59" s="64" t="s">
-        <v>73</v>
-      </c>
-      <c r="J59" s="64"/>
-      <c r="K59" s="64"/>
-      <c r="L59" s="64"/>
-      <c r="M59" s="64"/>
+      <c r="D59" s="67"/>
+      <c r="E59" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="F59" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="G59" s="70"/>
+      <c r="H59" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="I59" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="J59" s="67"/>
+      <c r="K59" s="67"/>
+      <c r="L59" s="67"/>
+      <c r="M59" s="67"/>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A60" s="64">
+      <c r="A60" s="67">
         <v>412.7</v>
       </c>
-      <c r="B60" s="63" t="s">
+      <c r="B60" s="66" t="s">
         <v>172</v>
       </c>
-      <c r="C60" s="63" t="s">
+      <c r="C60" s="66" t="s">
         <v>173</v>
       </c>
-      <c r="D60" s="64"/>
-      <c r="E60" s="64"/>
-      <c r="F60" s="64"/>
-      <c r="G60" s="67"/>
-      <c r="H60" s="64" t="s">
-        <v>73</v>
-      </c>
-      <c r="I60" s="64"/>
-      <c r="J60" s="64"/>
-      <c r="K60" s="64"/>
-      <c r="L60" s="64"/>
-      <c r="M60" s="64"/>
+      <c r="D60" s="67"/>
+      <c r="E60" s="67"/>
+      <c r="F60" s="67"/>
+      <c r="G60" s="70"/>
+      <c r="H60" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="I60" s="67"/>
+      <c r="J60" s="67"/>
+      <c r="K60" s="67"/>
+      <c r="L60" s="67"/>
+      <c r="M60" s="67"/>
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A61" s="64">
+      <c r="A61" s="67">
         <v>413</v>
       </c>
-      <c r="B61" s="63" t="s">
+      <c r="B61" s="66" t="s">
         <v>174</v>
       </c>
-      <c r="C61" s="63" t="s">
+      <c r="C61" s="66" t="s">
         <v>175</v>
       </c>
-      <c r="D61" s="64"/>
-      <c r="E61" s="65"/>
-      <c r="F61" s="65"/>
-      <c r="G61" s="66"/>
-      <c r="H61" s="65" t="s">
-        <v>73</v>
-      </c>
-      <c r="I61" s="65" t="s">
-        <v>73</v>
-      </c>
-      <c r="J61" s="65"/>
-      <c r="K61" s="65"/>
-      <c r="L61" s="65"/>
-      <c r="M61" s="65"/>
+      <c r="D61" s="67"/>
+      <c r="E61" s="68"/>
+      <c r="F61" s="68"/>
+      <c r="G61" s="69"/>
+      <c r="H61" s="68" t="s">
+        <v>73</v>
+      </c>
+      <c r="I61" s="68" t="s">
+        <v>73</v>
+      </c>
+      <c r="J61" s="68"/>
+      <c r="K61" s="68"/>
+      <c r="L61" s="68"/>
+      <c r="M61" s="68"/>
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A62" s="64">
+      <c r="A62" s="67">
         <v>411.1</v>
       </c>
-      <c r="B62" s="63" t="s">
+      <c r="B62" s="66" t="s">
         <v>176</v>
       </c>
-      <c r="C62" s="63" t="s">
+      <c r="C62" s="66" t="s">
         <v>177</v>
       </c>
-      <c r="D62" s="64"/>
-      <c r="E62" s="65"/>
-      <c r="F62" s="65"/>
-      <c r="G62" s="66"/>
-      <c r="H62" s="65"/>
-      <c r="I62" s="65"/>
-      <c r="J62" s="65"/>
-      <c r="K62" s="65"/>
-      <c r="L62" s="65"/>
-      <c r="M62" s="65"/>
+      <c r="D62" s="67"/>
+      <c r="E62" s="68"/>
+      <c r="F62" s="68"/>
+      <c r="G62" s="69"/>
+      <c r="H62" s="68"/>
+      <c r="I62" s="68"/>
+      <c r="J62" s="68"/>
+      <c r="K62" s="68"/>
+      <c r="L62" s="68"/>
+      <c r="M62" s="68"/>
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A63" s="64">
+      <c r="A63" s="67">
         <v>414</v>
       </c>
-      <c r="B63" s="63" t="s">
+      <c r="B63" s="66" t="s">
         <v>178</v>
       </c>
-      <c r="C63" s="63" t="s">
+      <c r="C63" s="66" t="s">
         <v>179</v>
       </c>
-      <c r="D63" s="64"/>
-      <c r="E63" s="65" t="s">
-        <v>73</v>
-      </c>
-      <c r="F63" s="65"/>
-      <c r="G63" s="66"/>
-      <c r="H63" s="65"/>
-      <c r="I63" s="65"/>
-      <c r="J63" s="65"/>
-      <c r="K63" s="65"/>
-      <c r="L63" s="65"/>
-      <c r="M63" s="65"/>
+      <c r="D63" s="67"/>
+      <c r="E63" s="68" t="s">
+        <v>73</v>
+      </c>
+      <c r="F63" s="68"/>
+      <c r="G63" s="69"/>
+      <c r="H63" s="68"/>
+      <c r="I63" s="68"/>
+      <c r="J63" s="68"/>
+      <c r="K63" s="68"/>
+      <c r="L63" s="68"/>
+      <c r="M63" s="68"/>
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A64" s="64">
+      <c r="A64" s="67">
         <v>412.1</v>
       </c>
-      <c r="B64" s="63" t="s">
+      <c r="B64" s="66" t="s">
         <v>176</v>
       </c>
-      <c r="C64" s="63" t="s">
+      <c r="C64" s="66" t="s">
         <v>180</v>
       </c>
-      <c r="D64" s="64"/>
-      <c r="E64" s="65"/>
-      <c r="F64" s="65"/>
-      <c r="G64" s="66"/>
-      <c r="H64" s="65"/>
-      <c r="I64" s="65"/>
-      <c r="J64" s="65"/>
-      <c r="K64" s="65"/>
-      <c r="L64" s="65"/>
-      <c r="M64" s="65"/>
+      <c r="D64" s="67"/>
+      <c r="E64" s="68"/>
+      <c r="F64" s="68"/>
+      <c r="G64" s="69"/>
+      <c r="H64" s="68"/>
+      <c r="I64" s="68"/>
+      <c r="J64" s="68"/>
+      <c r="K64" s="68"/>
+      <c r="L64" s="68"/>
+      <c r="M64" s="68"/>
     </row>
     <row r="65" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A65" s="64">
+      <c r="A65" s="67">
         <v>415</v>
       </c>
-      <c r="B65" s="63" t="s">
+      <c r="B65" s="66" t="s">
         <v>181</v>
       </c>
-      <c r="C65" s="63" t="s">
+      <c r="C65" s="66" t="s">
         <v>182</v>
       </c>
-      <c r="D65" s="64"/>
-      <c r="E65" s="65" t="s">
-        <v>73</v>
-      </c>
-      <c r="F65" s="65"/>
-      <c r="G65" s="66"/>
-      <c r="H65" s="65" t="s">
-        <v>73</v>
-      </c>
-      <c r="I65" s="65" t="s">
-        <v>73</v>
-      </c>
-      <c r="J65" s="65"/>
-      <c r="K65" s="65"/>
-      <c r="L65" s="65"/>
-      <c r="M65" s="65"/>
+      <c r="D65" s="67"/>
+      <c r="E65" s="68" t="s">
+        <v>73</v>
+      </c>
+      <c r="F65" s="68"/>
+      <c r="G65" s="69"/>
+      <c r="H65" s="68" t="s">
+        <v>73</v>
+      </c>
+      <c r="I65" s="68" t="s">
+        <v>73</v>
+      </c>
+      <c r="J65" s="68"/>
+      <c r="K65" s="68"/>
+      <c r="L65" s="68"/>
+      <c r="M65" s="68"/>
     </row>
     <row r="66" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A66" s="64">
+      <c r="A66" s="67">
         <v>413.1</v>
       </c>
-      <c r="B66" s="63" t="s">
+      <c r="B66" s="66" t="s">
         <v>183</v>
       </c>
-      <c r="C66" s="63" t="s">
+      <c r="C66" s="66" t="s">
         <v>184</v>
       </c>
-      <c r="D66" s="64"/>
-      <c r="E66" s="65"/>
-      <c r="F66" s="65"/>
-      <c r="G66" s="66"/>
-      <c r="H66" s="65"/>
-      <c r="I66" s="65"/>
-      <c r="J66" s="65"/>
-      <c r="K66" s="65"/>
-      <c r="L66" s="65"/>
-      <c r="M66" s="65"/>
+      <c r="D66" s="67"/>
+      <c r="E66" s="68"/>
+      <c r="F66" s="68"/>
+      <c r="G66" s="69"/>
+      <c r="H66" s="68"/>
+      <c r="I66" s="68"/>
+      <c r="J66" s="68"/>
+      <c r="K66" s="68"/>
+      <c r="L66" s="68"/>
+      <c r="M66" s="68"/>
     </row>
     <row r="67" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A67" s="64">
+      <c r="A67" s="67">
         <v>502</v>
       </c>
-      <c r="B67" s="63" t="s">
+      <c r="B67" s="66" t="s">
         <v>185</v>
       </c>
-      <c r="C67" s="63" t="s">
+      <c r="C67" s="66" t="s">
         <v>186</v>
       </c>
-      <c r="D67" s="64"/>
-      <c r="E67" s="65" t="s">
+      <c r="D67" s="67"/>
+      <c r="E67" s="68" t="s">
         <v>68</v>
       </c>
-      <c r="F67" s="65" t="s">
+      <c r="F67" s="68" t="s">
         <v>68</v>
       </c>
-      <c r="G67" s="66"/>
-      <c r="H67" s="65" t="s">
-        <v>73</v>
-      </c>
-      <c r="I67" s="65" t="s">
-        <v>73</v>
-      </c>
-      <c r="J67" s="65"/>
-      <c r="K67" s="65" t="s">
-        <v>73</v>
-      </c>
-      <c r="L67" s="65" t="s">
-        <v>73</v>
-      </c>
-      <c r="M67" s="65"/>
+      <c r="G67" s="69"/>
+      <c r="H67" s="68" t="s">
+        <v>73</v>
+      </c>
+      <c r="I67" s="68" t="s">
+        <v>73</v>
+      </c>
+      <c r="J67" s="68"/>
+      <c r="K67" s="68" t="s">
+        <v>73</v>
+      </c>
+      <c r="L67" s="68" t="s">
+        <v>73</v>
+      </c>
+      <c r="M67" s="68"/>
     </row>
     <row r="68" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A68" s="64">
+      <c r="A68" s="67">
         <v>502.1</v>
       </c>
-      <c r="B68" s="63" t="s">
+      <c r="B68" s="66" t="s">
         <v>66</v>
       </c>
-      <c r="C68" s="63" t="s">
+      <c r="C68" s="66" t="s">
         <v>124</v>
       </c>
-      <c r="D68" s="64"/>
-      <c r="E68" s="65"/>
-      <c r="F68" s="65"/>
-      <c r="G68" s="66"/>
-      <c r="H68" s="65"/>
-      <c r="I68" s="65"/>
-      <c r="J68" s="65"/>
-      <c r="K68" s="65"/>
-      <c r="L68" s="65"/>
-      <c r="M68" s="65"/>
+      <c r="D68" s="67"/>
+      <c r="E68" s="68"/>
+      <c r="F68" s="68"/>
+      <c r="G68" s="69"/>
+      <c r="H68" s="68"/>
+      <c r="I68" s="68"/>
+      <c r="J68" s="68"/>
+      <c r="K68" s="68"/>
+      <c r="L68" s="68"/>
+      <c r="M68" s="68"/>
     </row>
     <row r="69" spans="1:13" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A69" s="64">
+      <c r="A69" s="67">
         <v>502.2</v>
       </c>
-      <c r="B69" s="63" t="s">
+      <c r="B69" s="66" t="s">
         <v>187</v>
       </c>
-      <c r="C69" s="63" t="s">
+      <c r="C69" s="66" t="s">
         <v>188</v>
       </c>
-      <c r="D69" s="64"/>
-      <c r="E69" s="64" t="s">
-        <v>73</v>
-      </c>
-      <c r="F69" s="64"/>
-      <c r="G69" s="67"/>
-      <c r="H69" s="64" t="s">
-        <v>73</v>
-      </c>
-      <c r="I69" s="64" t="s">
-        <v>73</v>
-      </c>
-      <c r="J69" s="64"/>
-      <c r="K69" s="64" t="s">
-        <v>73</v>
-      </c>
-      <c r="L69" s="64" t="s">
-        <v>73</v>
-      </c>
-      <c r="M69" s="64"/>
+      <c r="D69" s="67"/>
+      <c r="E69" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="F69" s="67"/>
+      <c r="G69" s="70"/>
+      <c r="H69" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="I69" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="J69" s="67"/>
+      <c r="K69" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="L69" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="M69" s="67"/>
     </row>
     <row r="70" spans="1:13" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A70" s="64">
+      <c r="A70" s="67">
         <v>502.3</v>
       </c>
-      <c r="B70" s="63" t="s">
+      <c r="B70" s="66" t="s">
         <v>187</v>
       </c>
-      <c r="C70" s="63" t="s">
+      <c r="C70" s="66" t="s">
         <v>189</v>
       </c>
-      <c r="D70" s="64"/>
-      <c r="E70" s="64" t="s">
-        <v>73</v>
-      </c>
-      <c r="F70" s="64"/>
-      <c r="G70" s="67"/>
-      <c r="H70" s="64"/>
-      <c r="I70" s="64"/>
-      <c r="J70" s="64"/>
-      <c r="K70" s="64" t="s">
-        <v>73</v>
-      </c>
-      <c r="L70" s="64" t="s">
-        <v>73</v>
-      </c>
-      <c r="M70" s="64"/>
+      <c r="D70" s="67"/>
+      <c r="E70" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="F70" s="67"/>
+      <c r="G70" s="70"/>
+      <c r="H70" s="67"/>
+      <c r="I70" s="67"/>
+      <c r="J70" s="67"/>
+      <c r="K70" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="L70" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="M70" s="67"/>
     </row>
     <row r="71" spans="1:13" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A71" s="64">
+      <c r="A71" s="67">
         <v>502.4</v>
       </c>
-      <c r="B71" s="63" t="s">
+      <c r="B71" s="66" t="s">
         <v>190</v>
       </c>
-      <c r="C71" s="63" t="s">
+      <c r="C71" s="66" t="s">
         <v>191</v>
       </c>
-      <c r="D71" s="64"/>
-      <c r="E71" s="64" t="s">
-        <v>73</v>
-      </c>
-      <c r="F71" s="64" t="s">
-        <v>73</v>
-      </c>
-      <c r="G71" s="67"/>
-      <c r="H71" s="64" t="s">
-        <v>73</v>
-      </c>
-      <c r="I71" s="64" t="s">
-        <v>73</v>
-      </c>
-      <c r="J71" s="64"/>
-      <c r="K71" s="64" t="s">
-        <v>73</v>
-      </c>
-      <c r="L71" s="64" t="s">
-        <v>73</v>
-      </c>
-      <c r="M71" s="64"/>
+      <c r="D71" s="67"/>
+      <c r="E71" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="F71" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="G71" s="70"/>
+      <c r="H71" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="I71" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="J71" s="67"/>
+      <c r="K71" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="L71" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="M71" s="67"/>
     </row>
     <row r="72" spans="1:13" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A72" s="64" t="s">
+      <c r="A72" s="67" t="s">
         <v>192</v>
       </c>
-      <c r="B72" s="63" t="s">
+      <c r="B72" s="66" t="s">
         <v>193</v>
       </c>
-      <c r="C72" s="63" t="s">
+      <c r="C72" s="66" t="s">
         <v>194</v>
       </c>
-      <c r="D72" s="64"/>
-      <c r="E72" s="64"/>
-      <c r="F72" s="64"/>
-      <c r="G72" s="67"/>
-      <c r="H72" s="64"/>
-      <c r="I72" s="64"/>
-      <c r="J72" s="64"/>
-      <c r="K72" s="64" t="s">
-        <v>73</v>
-      </c>
-      <c r="L72" s="64" t="s">
-        <v>73</v>
-      </c>
-      <c r="M72" s="64"/>
+      <c r="D72" s="67"/>
+      <c r="E72" s="67"/>
+      <c r="F72" s="67"/>
+      <c r="G72" s="70"/>
+      <c r="H72" s="67"/>
+      <c r="I72" s="67"/>
+      <c r="J72" s="67"/>
+      <c r="K72" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="L72" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="M72" s="67"/>
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A73" s="64" t="s">
+      <c r="A73" s="67" t="s">
         <v>195</v>
       </c>
-      <c r="B73" s="63" t="s">
+      <c r="B73" s="66" t="s">
         <v>196</v>
       </c>
-      <c r="C73" s="63" t="s">
+      <c r="C73" s="66" t="s">
         <v>197</v>
       </c>
-      <c r="D73" s="64"/>
-      <c r="E73" s="64"/>
-      <c r="F73" s="64"/>
-      <c r="G73" s="67"/>
-      <c r="H73" s="64"/>
-      <c r="I73" s="64"/>
-      <c r="J73" s="64"/>
-      <c r="K73" s="64" t="s">
-        <v>73</v>
-      </c>
-      <c r="L73" s="64" t="s">
-        <v>73</v>
-      </c>
-      <c r="M73" s="64"/>
+      <c r="D73" s="67"/>
+      <c r="E73" s="67"/>
+      <c r="F73" s="67"/>
+      <c r="G73" s="70"/>
+      <c r="H73" s="67"/>
+      <c r="I73" s="67"/>
+      <c r="J73" s="67"/>
+      <c r="K73" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="L73" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="M73" s="67"/>
     </row>
     <row r="74" spans="1:13" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A74" s="64" t="s">
+      <c r="A74" s="67" t="s">
         <v>198</v>
       </c>
-      <c r="B74" s="63" t="s">
+      <c r="B74" s="66" t="s">
         <v>199</v>
       </c>
-      <c r="C74" s="63" t="s">
+      <c r="C74" s="66" t="s">
         <v>200</v>
       </c>
-      <c r="D74" s="64"/>
-      <c r="E74" s="64"/>
-      <c r="F74" s="64"/>
-      <c r="G74" s="67"/>
-      <c r="H74" s="64"/>
-      <c r="I74" s="64"/>
-      <c r="J74" s="64"/>
-      <c r="K74" s="64" t="s">
-        <v>73</v>
-      </c>
-      <c r="L74" s="64" t="s">
-        <v>73</v>
-      </c>
-      <c r="M74" s="64"/>
+      <c r="D74" s="67"/>
+      <c r="E74" s="67"/>
+      <c r="F74" s="67"/>
+      <c r="G74" s="70"/>
+      <c r="H74" s="67"/>
+      <c r="I74" s="67"/>
+      <c r="J74" s="67"/>
+      <c r="K74" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="L74" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="M74" s="67"/>
     </row>
     <row r="75" spans="1:13" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A75" s="64" t="s">
+      <c r="A75" s="67" t="s">
         <v>201</v>
       </c>
-      <c r="B75" s="63" t="s">
+      <c r="B75" s="66" t="s">
         <v>202</v>
       </c>
-      <c r="C75" s="63" t="s">
+      <c r="C75" s="66" t="s">
         <v>203</v>
       </c>
-      <c r="D75" s="64"/>
-      <c r="E75" s="64"/>
-      <c r="F75" s="64"/>
-      <c r="G75" s="67"/>
-      <c r="H75" s="64" t="s">
-        <v>73</v>
-      </c>
-      <c r="I75" s="64" t="s">
-        <v>73</v>
-      </c>
-      <c r="J75" s="64"/>
-      <c r="K75" s="64"/>
-      <c r="L75" s="64"/>
-      <c r="M75" s="64"/>
+      <c r="D75" s="67"/>
+      <c r="E75" s="67"/>
+      <c r="F75" s="67"/>
+      <c r="G75" s="70"/>
+      <c r="H75" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="I75" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="J75" s="67"/>
+      <c r="K75" s="67"/>
+      <c r="L75" s="67"/>
+      <c r="M75" s="67"/>
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A76" s="64" t="s">
+      <c r="A76" s="67" t="s">
         <v>204</v>
       </c>
-      <c r="B76" s="63" t="s">
+      <c r="B76" s="66" t="s">
         <v>205</v>
       </c>
-      <c r="C76" s="63" t="s">
+      <c r="C76" s="66" t="s">
         <v>206</v>
       </c>
-      <c r="D76" s="64"/>
-      <c r="E76" s="64"/>
-      <c r="F76" s="64" t="s">
-        <v>73</v>
-      </c>
-      <c r="G76" s="67"/>
-      <c r="H76" s="64"/>
-      <c r="I76" s="64" t="s">
-        <v>73</v>
-      </c>
-      <c r="J76" s="64"/>
-      <c r="K76" s="64"/>
-      <c r="L76" s="64"/>
-      <c r="M76" s="64"/>
+      <c r="D76" s="67"/>
+      <c r="E76" s="67"/>
+      <c r="F76" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="G76" s="70"/>
+      <c r="H76" s="67"/>
+      <c r="I76" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="J76" s="67"/>
+      <c r="K76" s="67"/>
+      <c r="L76" s="67"/>
+      <c r="M76" s="67"/>
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A77" s="64" t="s">
+      <c r="A77" s="67" t="s">
         <v>207</v>
       </c>
-      <c r="B77" s="63" t="s">
+      <c r="B77" s="66" t="s">
         <v>208</v>
       </c>
-      <c r="C77" s="63" t="s">
+      <c r="C77" s="66" t="s">
         <v>209</v>
       </c>
-      <c r="D77" s="64"/>
-      <c r="E77" s="64" t="s">
-        <v>73</v>
-      </c>
-      <c r="F77" s="64" t="s">
-        <v>73</v>
-      </c>
-      <c r="G77" s="67"/>
-      <c r="H77" s="64"/>
-      <c r="I77" s="64"/>
-      <c r="J77" s="64" t="s">
-        <v>73</v>
-      </c>
-      <c r="K77" s="64"/>
-      <c r="L77" s="64"/>
-      <c r="M77" s="64"/>
+      <c r="D77" s="67"/>
+      <c r="E77" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="F77" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="G77" s="70"/>
+      <c r="H77" s="67"/>
+      <c r="I77" s="67"/>
+      <c r="J77" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="K77" s="67"/>
+      <c r="L77" s="67"/>
+      <c r="M77" s="67"/>
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A78" s="64" t="s">
+      <c r="A78" s="67" t="s">
         <v>210</v>
       </c>
-      <c r="B78" s="63" t="s">
+      <c r="B78" s="66" t="s">
         <v>211</v>
       </c>
-      <c r="C78" s="63" t="s">
+      <c r="C78" s="66" t="s">
         <v>212</v>
       </c>
-      <c r="D78" s="64"/>
-      <c r="E78" s="64"/>
-      <c r="F78" s="64"/>
-      <c r="G78" s="67"/>
-      <c r="H78" s="64" t="s">
-        <v>73</v>
-      </c>
-      <c r="I78" s="64" t="s">
-        <v>73</v>
-      </c>
-      <c r="J78" s="64"/>
-      <c r="K78" s="64"/>
-      <c r="L78" s="64"/>
-      <c r="M78" s="64"/>
+      <c r="D78" s="67"/>
+      <c r="E78" s="67"/>
+      <c r="F78" s="67"/>
+      <c r="G78" s="70"/>
+      <c r="H78" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="I78" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="J78" s="67"/>
+      <c r="K78" s="67"/>
+      <c r="L78" s="67"/>
+      <c r="M78" s="67"/>
     </row>
     <row r="79" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A79" s="64">
+      <c r="A79" s="67">
         <v>503</v>
       </c>
-      <c r="B79" s="63" t="s">
+      <c r="B79" s="66" t="s">
         <v>213</v>
       </c>
-      <c r="C79" s="63" t="s">
+      <c r="C79" s="66" t="s">
         <v>214</v>
       </c>
-      <c r="D79" s="64"/>
-      <c r="E79" s="65" t="s">
-        <v>73</v>
-      </c>
-      <c r="F79" s="65" t="s">
-        <v>73</v>
-      </c>
-      <c r="G79" s="66"/>
-      <c r="H79" s="65" t="s">
-        <v>73</v>
-      </c>
-      <c r="I79" s="65" t="s">
-        <v>73</v>
-      </c>
-      <c r="J79" s="65"/>
-      <c r="K79" s="65" t="s">
-        <v>73</v>
-      </c>
-      <c r="L79" s="65" t="s">
-        <v>73</v>
-      </c>
-      <c r="M79" s="65"/>
+      <c r="D79" s="67"/>
+      <c r="E79" s="68" t="s">
+        <v>73</v>
+      </c>
+      <c r="F79" s="68" t="s">
+        <v>73</v>
+      </c>
+      <c r="G79" s="69"/>
+      <c r="H79" s="68" t="s">
+        <v>73</v>
+      </c>
+      <c r="I79" s="68" t="s">
+        <v>73</v>
+      </c>
+      <c r="J79" s="68"/>
+      <c r="K79" s="68" t="s">
+        <v>73</v>
+      </c>
+      <c r="L79" s="68" t="s">
+        <v>73</v>
+      </c>
+      <c r="M79" s="68"/>
     </row>
     <row r="80" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A80" s="64">
+      <c r="A80" s="67">
         <v>503.1</v>
       </c>
-      <c r="B80" s="63" t="s">
+      <c r="B80" s="66" t="s">
         <v>123</v>
       </c>
-      <c r="C80" s="63" t="s">
+      <c r="C80" s="66" t="s">
         <v>124</v>
       </c>
-      <c r="D80" s="64"/>
-      <c r="E80" s="65"/>
-      <c r="F80" s="65"/>
-      <c r="G80" s="66"/>
-      <c r="H80" s="65"/>
-      <c r="I80" s="65"/>
-      <c r="J80" s="65"/>
-      <c r="K80" s="65"/>
-      <c r="L80" s="65"/>
-      <c r="M80" s="65"/>
+      <c r="D80" s="67"/>
+      <c r="E80" s="68"/>
+      <c r="F80" s="68"/>
+      <c r="G80" s="69"/>
+      <c r="H80" s="68"/>
+      <c r="I80" s="68"/>
+      <c r="J80" s="68"/>
+      <c r="K80" s="68"/>
+      <c r="L80" s="68"/>
+      <c r="M80" s="68"/>
     </row>
     <row r="81" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A81" s="64">
+      <c r="A81" s="67">
         <v>503.2</v>
       </c>
-      <c r="B81" s="63" t="s">
+      <c r="B81" s="66" t="s">
         <v>215</v>
       </c>
-      <c r="C81" s="63" t="s">
+      <c r="C81" s="66" t="s">
         <v>216</v>
       </c>
-      <c r="D81" s="64"/>
-      <c r="E81" s="64"/>
-      <c r="F81" s="64" t="s">
-        <v>73</v>
-      </c>
-      <c r="G81" s="67"/>
-      <c r="H81" s="64"/>
-      <c r="I81" s="64"/>
-      <c r="J81" s="64"/>
-      <c r="K81" s="64"/>
-      <c r="L81" s="64"/>
-      <c r="M81" s="64"/>
+      <c r="D81" s="67"/>
+      <c r="E81" s="67"/>
+      <c r="F81" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="G81" s="70"/>
+      <c r="H81" s="67"/>
+      <c r="I81" s="67"/>
+      <c r="J81" s="67"/>
+      <c r="K81" s="67"/>
+      <c r="L81" s="67"/>
+      <c r="M81" s="67"/>
     </row>
     <row r="82" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A82" s="64">
+      <c r="A82" s="67">
         <v>503.3</v>
       </c>
-      <c r="B82" s="63" t="s">
+      <c r="B82" s="66" t="s">
         <v>217</v>
       </c>
-      <c r="C82" s="63" t="s">
+      <c r="C82" s="66" t="s">
         <v>218</v>
       </c>
-      <c r="D82" s="64"/>
-      <c r="E82" s="64" t="s">
-        <v>73</v>
-      </c>
-      <c r="F82" s="64"/>
-      <c r="G82" s="67"/>
-      <c r="H82" s="64"/>
-      <c r="I82" s="64"/>
-      <c r="J82" s="64"/>
-      <c r="K82" s="64" t="s">
-        <v>73</v>
-      </c>
-      <c r="L82" s="64" t="s">
-        <v>73</v>
-      </c>
-      <c r="M82" s="64"/>
+      <c r="D82" s="67"/>
+      <c r="E82" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="F82" s="67"/>
+      <c r="G82" s="70"/>
+      <c r="H82" s="67"/>
+      <c r="I82" s="67"/>
+      <c r="J82" s="67"/>
+      <c r="K82" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="L82" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="M82" s="67"/>
     </row>
     <row r="83" spans="1:13" ht="54" x14ac:dyDescent="0.55000000000000004">
-      <c r="A83" s="64">
+      <c r="A83" s="67">
         <v>503.4</v>
       </c>
-      <c r="B83" s="63" t="s">
+      <c r="B83" s="66" t="s">
         <v>219</v>
       </c>
-      <c r="C83" s="63" t="s">
+      <c r="C83" s="66" t="s">
         <v>220</v>
       </c>
-      <c r="D83" s="64"/>
-      <c r="E83" s="64" t="s">
-        <v>73</v>
-      </c>
-      <c r="F83" s="64"/>
-      <c r="G83" s="67"/>
-      <c r="H83" s="64" t="s">
-        <v>73</v>
-      </c>
-      <c r="I83" s="64" t="s">
-        <v>73</v>
-      </c>
-      <c r="J83" s="64"/>
-      <c r="K83" s="64"/>
-      <c r="L83" s="64"/>
-      <c r="M83" s="64"/>
+      <c r="D83" s="67"/>
+      <c r="E83" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="F83" s="67"/>
+      <c r="G83" s="70"/>
+      <c r="H83" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="I83" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="J83" s="67"/>
+      <c r="K83" s="67"/>
+      <c r="L83" s="67"/>
+      <c r="M83" s="67"/>
     </row>
     <row r="84" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A84" s="64">
+      <c r="A84" s="67">
         <v>504</v>
       </c>
-      <c r="B84" s="63" t="s">
+      <c r="B84" s="66" t="s">
         <v>221</v>
       </c>
-      <c r="C84" s="63" t="s">
+      <c r="C84" s="66" t="s">
         <v>222</v>
       </c>
-      <c r="D84" s="64"/>
-      <c r="E84" s="65" t="s">
-        <v>73</v>
-      </c>
-      <c r="F84" s="65" t="s">
-        <v>73</v>
-      </c>
-      <c r="G84" s="66"/>
-      <c r="H84" s="65" t="s">
-        <v>73</v>
-      </c>
-      <c r="I84" s="65" t="s">
-        <v>73</v>
-      </c>
-      <c r="J84" s="65"/>
-      <c r="K84" s="65"/>
-      <c r="L84" s="65"/>
-      <c r="M84" s="65"/>
+      <c r="D84" s="67"/>
+      <c r="E84" s="68" t="s">
+        <v>73</v>
+      </c>
+      <c r="F84" s="68" t="s">
+        <v>73</v>
+      </c>
+      <c r="G84" s="69"/>
+      <c r="H84" s="68" t="s">
+        <v>73</v>
+      </c>
+      <c r="I84" s="68" t="s">
+        <v>73</v>
+      </c>
+      <c r="J84" s="68"/>
+      <c r="K84" s="68"/>
+      <c r="L84" s="68"/>
+      <c r="M84" s="68"/>
     </row>
     <row r="85" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A85" s="64">
+      <c r="A85" s="67">
         <v>504.1</v>
       </c>
-      <c r="B85" s="63" t="s">
+      <c r="B85" s="66" t="s">
         <v>123</v>
       </c>
-      <c r="C85" s="63" t="s">
+      <c r="C85" s="66" t="s">
         <v>127</v>
       </c>
-      <c r="D85" s="64"/>
-      <c r="E85" s="65"/>
-      <c r="F85" s="65"/>
-      <c r="G85" s="66"/>
-      <c r="H85" s="65"/>
-      <c r="I85" s="65"/>
-      <c r="J85" s="65"/>
-      <c r="K85" s="65"/>
-      <c r="L85" s="65"/>
-      <c r="M85" s="65"/>
+      <c r="D85" s="67"/>
+      <c r="E85" s="68"/>
+      <c r="F85" s="68"/>
+      <c r="G85" s="69"/>
+      <c r="H85" s="68"/>
+      <c r="I85" s="68"/>
+      <c r="J85" s="68"/>
+      <c r="K85" s="68"/>
+      <c r="L85" s="68"/>
+      <c r="M85" s="68"/>
     </row>
     <row r="86" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A86" s="64">
+      <c r="A86" s="67">
         <v>504.2</v>
       </c>
-      <c r="B86" s="63" t="s">
+      <c r="B86" s="66" t="s">
         <v>223</v>
       </c>
-      <c r="C86" s="63" t="s">
+      <c r="C86" s="66" t="s">
         <v>224</v>
       </c>
-      <c r="D86" s="64"/>
-      <c r="E86" s="64" t="s">
-        <v>73</v>
-      </c>
-      <c r="F86" s="64" t="s">
-        <v>73</v>
-      </c>
-      <c r="G86" s="67"/>
-      <c r="H86" s="64" t="s">
-        <v>73</v>
-      </c>
-      <c r="I86" s="64" t="s">
-        <v>73</v>
-      </c>
-      <c r="J86" s="64"/>
-      <c r="K86" s="64"/>
-      <c r="L86" s="64"/>
-      <c r="M86" s="64"/>
+      <c r="D86" s="67"/>
+      <c r="E86" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="F86" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="G86" s="70"/>
+      <c r="H86" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="I86" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="J86" s="67"/>
+      <c r="K86" s="67"/>
+      <c r="L86" s="67"/>
+      <c r="M86" s="67"/>
     </row>
     <row r="87" spans="1:13" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A87" s="64" t="s">
+      <c r="A87" s="67" t="s">
         <v>225</v>
       </c>
-      <c r="B87" s="63" t="s">
+      <c r="B87" s="66" t="s">
         <v>226</v>
       </c>
-      <c r="C87" s="63" t="s">
+      <c r="C87" s="66" t="s">
         <v>227</v>
       </c>
-      <c r="D87" s="64"/>
-      <c r="E87" s="64" t="s">
-        <v>73</v>
-      </c>
-      <c r="F87" s="64"/>
-      <c r="G87" s="67"/>
-      <c r="H87" s="64" t="s">
-        <v>73</v>
-      </c>
-      <c r="I87" s="64" t="s">
-        <v>73</v>
-      </c>
-      <c r="J87" s="64"/>
-      <c r="K87" s="64"/>
-      <c r="L87" s="64"/>
-      <c r="M87" s="64"/>
+      <c r="D87" s="67"/>
+      <c r="E87" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="F87" s="67"/>
+      <c r="G87" s="70"/>
+      <c r="H87" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="I87" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="J87" s="67"/>
+      <c r="K87" s="67"/>
+      <c r="L87" s="67"/>
+      <c r="M87" s="67"/>
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A88" s="64" t="s">
+      <c r="A88" s="67" t="s">
         <v>228</v>
       </c>
-      <c r="B88" s="63" t="s">
+      <c r="B88" s="66" t="s">
         <v>229</v>
       </c>
-      <c r="C88" s="63" t="s">
+      <c r="C88" s="66" t="s">
         <v>230</v>
       </c>
-      <c r="D88" s="64"/>
-      <c r="E88" s="64" t="s">
-        <v>73</v>
-      </c>
-      <c r="F88" s="64" t="s">
-        <v>73</v>
-      </c>
-      <c r="G88" s="67"/>
-      <c r="H88" s="64"/>
-      <c r="I88" s="64"/>
-      <c r="J88" s="64"/>
-      <c r="K88" s="64"/>
-      <c r="L88" s="64"/>
-      <c r="M88" s="64"/>
+      <c r="D88" s="67"/>
+      <c r="E88" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="F88" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="G88" s="70"/>
+      <c r="H88" s="67"/>
+      <c r="I88" s="67"/>
+      <c r="J88" s="67"/>
+      <c r="K88" s="67"/>
+      <c r="L88" s="67"/>
+      <c r="M88" s="67"/>
     </row>
     <row r="89" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A89" s="64">
+      <c r="A89" s="67">
         <v>504.3</v>
       </c>
-      <c r="B89" s="63" t="s">
+      <c r="B89" s="66" t="s">
         <v>231</v>
       </c>
-      <c r="C89" s="63" t="s">
+      <c r="C89" s="66" t="s">
         <v>232</v>
       </c>
-      <c r="D89" s="64"/>
-      <c r="E89" s="64" t="s">
-        <v>73</v>
-      </c>
-      <c r="F89" s="64" t="s">
-        <v>73</v>
-      </c>
-      <c r="G89" s="67"/>
-      <c r="H89" s="64" t="s">
-        <v>73</v>
-      </c>
-      <c r="I89" s="64" t="s">
-        <v>73</v>
-      </c>
-      <c r="J89" s="64"/>
-      <c r="K89" s="64"/>
-      <c r="L89" s="64"/>
-      <c r="M89" s="64"/>
+      <c r="D89" s="67"/>
+      <c r="E89" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="F89" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="G89" s="70"/>
+      <c r="H89" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="I89" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="J89" s="67"/>
+      <c r="K89" s="67"/>
+      <c r="L89" s="67"/>
+      <c r="M89" s="67"/>
     </row>
     <row r="90" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A90" s="64">
+      <c r="A90" s="67">
         <v>504.4</v>
       </c>
-      <c r="B90" s="63" t="s">
+      <c r="B90" s="66" t="s">
         <v>233</v>
       </c>
-      <c r="C90" s="63" t="s">
+      <c r="C90" s="66" t="s">
         <v>234</v>
       </c>
-      <c r="D90" s="64"/>
-      <c r="E90" s="64" t="s">
-        <v>73</v>
-      </c>
-      <c r="F90" s="64" t="s">
-        <v>73</v>
-      </c>
-      <c r="G90" s="67"/>
-      <c r="H90" s="64" t="s">
-        <v>73</v>
-      </c>
-      <c r="I90" s="64" t="s">
-        <v>73</v>
-      </c>
-      <c r="J90" s="64"/>
-      <c r="K90" s="64"/>
-      <c r="L90" s="64"/>
-      <c r="M90" s="64"/>
+      <c r="D90" s="67"/>
+      <c r="E90" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="F90" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="G90" s="70"/>
+      <c r="H90" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="I90" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="J90" s="67"/>
+      <c r="K90" s="67"/>
+      <c r="L90" s="67"/>
+      <c r="M90" s="67"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:M90" xr:uid="{C6D2D344-3C1F-449C-B697-53FB90F953F5}"/>
